--- a/Strings.xlsx
+++ b/Strings.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="9075" activeTab="5"/>
+    <workbookView windowWidth="21000" windowHeight="9075"/>
   </bookViews>
   <sheets>
     <sheet name="Text" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2508" uniqueCount="2313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2532" uniqueCount="2337">
   <si>
     <t>English</t>
   </si>
@@ -2203,6 +2203,33 @@
     <t>豺狼和跟班看到通风口的标记</t>
   </si>
   <si>
+    <t>doorOpenNumberOfUses</t>
+  </si>
+  <si>
+    <t>Number Of Pass Door Uses</t>
+  </si>
+  <si>
+    <t>穿门最大次数</t>
+  </si>
+  <si>
+    <t>doorOpenCooldown</t>
+  </si>
+  <si>
+    <t>Pass Door Cooldown</t>
+  </si>
+  <si>
+    <t>穿门技能冷却时间</t>
+  </si>
+  <si>
+    <t>doorOpenDuration</t>
+  </si>
+  <si>
+    <t>Pass Door Duration</t>
+  </si>
+  <si>
+    <t>穿门技能持续时间</t>
+  </si>
+  <si>
     <t>sheriff</t>
   </si>
   <si>
@@ -2515,13 +2542,40 @@
     <t>时间之盾冷却时间</t>
   </si>
   <si>
+    <t>timeMasterCanRewind</t>
+  </si>
+  <si>
+    <t>Time Master Can Use Rewind</t>
+  </si>
+  <si>
+    <t>时间之主可以主动回溯时间</t>
+  </si>
+  <si>
+    <t>timeMasterRewindCooldown</t>
+  </si>
+  <si>
+    <t>Time Master Rewind Cooldown</t>
+  </si>
+  <si>
+    <t>时间之主主动回溯技能冷却</t>
+  </si>
+  <si>
+    <t>timeMasterReviveDuringRewind</t>
+  </si>
+  <si>
+    <t>Tme Master Rewind Can Revive Player</t>
+  </si>
+  <si>
+    <t>时间之主可以复活已死亡玩家</t>
+  </si>
+  <si>
     <t>timeMasterRewindTime</t>
   </si>
   <si>
     <t>Rewind Time</t>
   </si>
   <si>
-    <t>时光之盾回溯时长</t>
+    <t>回溯时长</t>
   </si>
   <si>
     <t>timeMasterShieldDuration</t>
@@ -6493,6 +6547,24 @@
   </si>
   <si>
     <t>踢出</t>
+  </si>
+  <si>
+    <t>engineerOpenDoorButtonText</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>穿过</t>
+  </si>
+  <si>
+    <t>timeMasterRewind</t>
+  </si>
+  <si>
+    <t>Rewind</t>
+  </si>
+  <si>
+    <t>回溯时间</t>
   </si>
   <si>
     <t>updatingText</t>
@@ -8261,7 +8333,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AK886"/>
+  <dimension ref="A1:AK892"/>
   <sheetFormatPr defaultColWidth="14.4285714285714" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="50.1428571428571" style="2" customWidth="1"/>
@@ -11500,68 +11572,74 @@
         <v>721</v>
       </c>
     </row>
-    <row r="318" spans="1:2">
-      <c r="A318" s="14"/>
-      <c r="B318" s="14"/>
+    <row r="318" spans="1:15">
+      <c r="A318" s="14" t="s">
+        <v>722</v>
+      </c>
+      <c r="B318" s="14" t="s">
+        <v>723</v>
+      </c>
+      <c r="O318" s="13" t="s">
+        <v>724</v>
+      </c>
     </row>
     <row r="319" spans="1:15">
       <c r="A319" s="14" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="B319" s="14" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="O319" s="13" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
     </row>
     <row r="320" spans="1:15">
       <c r="A320" s="14" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="B320" s="14" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="O320" s="13" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="321" spans="1:15">
-      <c r="A321" s="14" t="s">
-        <v>728</v>
-      </c>
-      <c r="B321" s="14" t="s">
-        <v>729</v>
-      </c>
-      <c r="O321" s="13" t="s">
         <v>730</v>
       </c>
     </row>
+    <row r="321" spans="1:2">
+      <c r="A321" s="14"/>
+      <c r="B321" s="14"/>
+    </row>
     <row r="322" spans="1:15">
-      <c r="A322" s="14"/>
-      <c r="B322" s="14"/>
-      <c r="O322" s="13"/>
+      <c r="A322" s="14" t="s">
+        <v>731</v>
+      </c>
+      <c r="B322" s="14" t="s">
+        <v>732</v>
+      </c>
+      <c r="O322" s="13" t="s">
+        <v>733</v>
+      </c>
     </row>
     <row r="323" spans="1:15">
       <c r="A323" s="14" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="B323" s="14" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="O323" s="13" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
     </row>
     <row r="324" spans="1:15">
       <c r="A324" s="14" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="B324" s="14" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="O324" s="13" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
     </row>
     <row r="325" spans="1:15">
@@ -11571,73 +11649,67 @@
     </row>
     <row r="326" spans="1:15">
       <c r="A326" s="14" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="B326" s="14" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="O326" s="13" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
     </row>
     <row r="327" spans="1:15">
       <c r="A327" s="14" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="B327" s="14" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="O327" s="13" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
     </row>
     <row r="328" spans="1:15">
-      <c r="A328" s="14" t="s">
-        <v>743</v>
-      </c>
-      <c r="B328" s="14" t="s">
-        <v>744</v>
-      </c>
-      <c r="O328" s="13" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="329" spans="1:2">
-      <c r="A329" s="14"/>
-      <c r="B329" s="14"/>
+      <c r="A328" s="14"/>
+      <c r="B328" s="14"/>
+      <c r="O328" s="13"/>
+    </row>
+    <row r="329" spans="1:15">
+      <c r="A329" s="14" t="s">
+        <v>746</v>
+      </c>
+      <c r="B329" s="14" t="s">
+        <v>747</v>
+      </c>
+      <c r="O329" s="13" t="s">
+        <v>748</v>
+      </c>
     </row>
     <row r="330" spans="1:15">
       <c r="A330" s="14" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="B330" s="14" t="s">
-        <v>747</v>
-      </c>
-      <c r="O330" s="2" t="s">
-        <v>748</v>
+        <v>750</v>
+      </c>
+      <c r="O330" s="13" t="s">
+        <v>751</v>
       </c>
     </row>
     <row r="331" spans="1:15">
       <c r="A331" s="14" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="B331" s="14" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="O331" s="13" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="332" spans="1:15">
-      <c r="A332" s="14" t="s">
-        <v>752</v>
-      </c>
-      <c r="B332" s="14" t="s">
-        <v>753</v>
-      </c>
-      <c r="O332" s="13" t="s">
         <v>754</v>
       </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332" s="14"/>
+      <c r="B332" s="14"/>
     </row>
     <row r="333" spans="1:15">
       <c r="A333" s="14" t="s">
@@ -11646,7 +11718,7 @@
       <c r="B333" s="14" t="s">
         <v>756</v>
       </c>
-      <c r="O333" s="13" t="s">
+      <c r="O333" s="2" t="s">
         <v>757</v>
       </c>
     </row>
@@ -11677,195 +11749,195 @@
         <v>764</v>
       </c>
       <c r="B336" s="14" t="s">
-        <v>17</v>
+        <v>765</v>
       </c>
       <c r="O336" s="13" t="s">
-        <v>18</v>
+        <v>766</v>
       </c>
     </row>
     <row r="337" spans="1:15">
       <c r="A337" s="14" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="B337" s="14" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="O337" s="13" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
     </row>
     <row r="338" spans="1:15">
       <c r="A338" s="14" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B338" s="14" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="O338" s="13" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
     </row>
     <row r="339" spans="1:15">
       <c r="A339" s="14" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B339" s="14" t="s">
-        <v>772</v>
-      </c>
-      <c r="O339" s="2" t="s">
-        <v>773</v>
+        <v>17</v>
+      </c>
+      <c r="O339" s="13" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="340" spans="1:15">
-      <c r="A340" s="14"/>
-      <c r="B340" s="14"/>
-      <c r="O340" s="13"/>
+      <c r="A340" s="14" t="s">
+        <v>774</v>
+      </c>
+      <c r="B340" s="14" t="s">
+        <v>775</v>
+      </c>
+      <c r="O340" s="13" t="s">
+        <v>776</v>
+      </c>
     </row>
     <row r="341" spans="1:15">
       <c r="A341" s="14" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="B341" s="14" t="s">
-        <v>775</v>
-      </c>
-      <c r="O341" s="7" t="s">
-        <v>776</v>
+        <v>778</v>
+      </c>
+      <c r="O341" s="13" t="s">
+        <v>779</v>
       </c>
     </row>
     <row r="342" spans="1:15">
       <c r="A342" s="14" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="B342" s="14" t="s">
-        <v>778</v>
-      </c>
-      <c r="O342" s="7" t="s">
-        <v>779</v>
+        <v>781</v>
+      </c>
+      <c r="O342" s="2" t="s">
+        <v>782</v>
       </c>
     </row>
     <row r="343" spans="1:15">
-      <c r="A343" s="14" t="s">
-        <v>780</v>
-      </c>
-      <c r="B343" s="14" t="s">
-        <v>778</v>
-      </c>
-      <c r="O343" s="7" t="s">
-        <v>779</v>
-      </c>
+      <c r="A343" s="14"/>
+      <c r="B343" s="14"/>
+      <c r="O343" s="13"/>
     </row>
     <row r="344" spans="1:15">
-      <c r="A344" s="14"/>
-      <c r="B344" s="14"/>
-      <c r="O344" s="7"/>
+      <c r="A344" s="14" t="s">
+        <v>783</v>
+      </c>
+      <c r="B344" s="14" t="s">
+        <v>784</v>
+      </c>
+      <c r="O344" s="7" t="s">
+        <v>785</v>
+      </c>
     </row>
     <row r="345" spans="1:15">
       <c r="A345" s="14" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="B345" s="14" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="O345" s="7" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
     </row>
     <row r="346" spans="1:15">
       <c r="A346" s="14" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="B346" s="14" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="O346" s="7" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
     </row>
     <row r="347" spans="1:15">
-      <c r="A347" s="14" t="s">
-        <v>787</v>
-      </c>
-      <c r="B347" s="14" t="s">
-        <v>788</v>
-      </c>
-      <c r="O347" s="7" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="348" spans="1:2">
-      <c r="A348" s="14"/>
-      <c r="B348" s="14"/>
+      <c r="A347" s="14"/>
+      <c r="B347" s="14"/>
+      <c r="O347" s="7"/>
+    </row>
+    <row r="348" spans="1:15">
+      <c r="A348" s="14" t="s">
+        <v>790</v>
+      </c>
+      <c r="B348" s="14" t="s">
+        <v>791</v>
+      </c>
+      <c r="O348" s="7" t="s">
+        <v>792</v>
+      </c>
     </row>
     <row r="349" spans="1:15">
       <c r="A349" s="14" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="B349" s="14" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="O349" s="7" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
     </row>
     <row r="350" spans="1:15">
       <c r="A350" s="14" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="B350" s="14" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="O350" s="7" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="351" spans="1:15">
-      <c r="A351" s="14" t="s">
-        <v>796</v>
-      </c>
-      <c r="B351" s="14" t="s">
-        <v>797</v>
-      </c>
-      <c r="O351" s="7" t="s">
         <v>798</v>
       </c>
     </row>
+    <row r="351" spans="1:2">
+      <c r="A351" s="14"/>
+      <c r="B351" s="14"/>
+    </row>
     <row r="352" spans="1:15">
-      <c r="A352" s="14"/>
-      <c r="B352" s="14"/>
-      <c r="O352" s="7"/>
+      <c r="A352" s="14" t="s">
+        <v>799</v>
+      </c>
+      <c r="B352" s="14" t="s">
+        <v>800</v>
+      </c>
+      <c r="O352" s="7" t="s">
+        <v>801</v>
+      </c>
     </row>
     <row r="353" spans="1:15">
       <c r="A353" s="14" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="B353" s="14" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="O353" s="7" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
     </row>
     <row r="354" spans="1:15">
       <c r="A354" s="14" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B354" s="14" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="O354" s="7" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
     </row>
     <row r="355" spans="1:15">
-      <c r="A355" s="14" t="s">
-        <v>805</v>
-      </c>
-      <c r="B355" s="14" t="s">
-        <v>806</v>
-      </c>
-      <c r="O355" s="7" t="s">
-        <v>807</v>
-      </c>
+      <c r="A355" s="14"/>
+      <c r="B355" s="14"/>
+      <c r="O355" s="7"/>
     </row>
     <row r="356" spans="1:15">
       <c r="A356" s="14" t="s">
@@ -11889,641 +11961,641 @@
         <v>813</v>
       </c>
     </row>
-    <row r="358" spans="1:2">
-      <c r="A358" s="14"/>
-      <c r="B358" s="14"/>
+    <row r="358" spans="1:15">
+      <c r="A358" s="14" t="s">
+        <v>814</v>
+      </c>
+      <c r="B358" s="14" t="s">
+        <v>815</v>
+      </c>
+      <c r="O358" s="7" t="s">
+        <v>816</v>
+      </c>
     </row>
     <row r="359" spans="1:15">
       <c r="A359" s="14" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="B359" s="14" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="O359" s="7" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
     </row>
     <row r="360" spans="1:15">
       <c r="A360" s="14" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="B360" s="14" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="O360" s="7" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="361" spans="1:15">
-      <c r="A361" s="14" t="s">
-        <v>820</v>
-      </c>
-      <c r="B361" s="14" t="s">
-        <v>821</v>
-      </c>
-      <c r="O361" s="7" t="s">
         <v>822</v>
       </c>
     </row>
+    <row r="361" spans="1:2">
+      <c r="A361" s="14"/>
+      <c r="B361" s="14"/>
+    </row>
     <row r="362" spans="1:15">
-      <c r="A362" s="14"/>
-      <c r="B362" s="14"/>
-      <c r="O362" s="7"/>
+      <c r="A362" s="14" t="s">
+        <v>823</v>
+      </c>
+      <c r="B362" s="14" t="s">
+        <v>824</v>
+      </c>
+      <c r="O362" s="7" t="s">
+        <v>825</v>
+      </c>
     </row>
     <row r="363" spans="1:15">
       <c r="A363" s="14" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="B363" s="14" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="O363" s="7" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
     </row>
     <row r="364" spans="1:15">
       <c r="A364" s="14" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="B364" s="14" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="O364" s="7" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
     </row>
     <row r="365" spans="1:15">
-      <c r="A365" s="14" t="s">
-        <v>829</v>
-      </c>
-      <c r="B365" s="14" t="s">
-        <v>830</v>
-      </c>
-      <c r="O365" s="7" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="366" spans="1:2">
-      <c r="A366" s="14"/>
-      <c r="B366" s="14"/>
+      <c r="A365" s="14"/>
+      <c r="B365" s="14"/>
+      <c r="O365" s="7"/>
+    </row>
+    <row r="366" spans="1:15">
+      <c r="A366" s="14" t="s">
+        <v>832</v>
+      </c>
+      <c r="B366" s="14" t="s">
+        <v>833</v>
+      </c>
+      <c r="O366" s="7" t="s">
+        <v>834</v>
+      </c>
     </row>
     <row r="367" spans="1:15">
       <c r="A367" s="14" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="B367" s="14" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="O367" s="7" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
     </row>
     <row r="368" spans="1:15">
       <c r="A368" s="14" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="B368" s="14" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="O368" s="7" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
     </row>
     <row r="369" spans="1:15">
       <c r="A369" s="14" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="B369" s="14" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="O369" s="7" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
     </row>
     <row r="370" spans="1:15">
-      <c r="A370" s="14"/>
-      <c r="B370" s="14"/>
-      <c r="O370" s="7"/>
+      <c r="A370" s="14" t="s">
+        <v>844</v>
+      </c>
+      <c r="B370" s="14" t="s">
+        <v>845</v>
+      </c>
+      <c r="O370" s="7" t="s">
+        <v>846</v>
+      </c>
     </row>
     <row r="371" spans="1:15">
       <c r="A371" s="14" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="B371" s="14" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="O371" s="7" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="372" spans="1:15">
-      <c r="A372" s="14" t="s">
-        <v>844</v>
-      </c>
-      <c r="B372" s="14" t="s">
-        <v>845</v>
-      </c>
-      <c r="O372" s="7" t="s">
-        <v>846</v>
-      </c>
+        <v>849</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" s="14"/>
+      <c r="B372" s="14"/>
     </row>
     <row r="373" spans="1:15">
       <c r="A373" s="14" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="B373" s="14" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="O373" s="7" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
     </row>
     <row r="374" spans="1:15">
       <c r="A374" s="14" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B374" s="14" t="s">
-        <v>833</v>
+        <v>854</v>
       </c>
       <c r="O374" s="7" t="s">
-        <v>834</v>
+        <v>855</v>
       </c>
     </row>
     <row r="375" spans="1:15">
       <c r="A375" s="14" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="B375" s="14" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="O375" s="7" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
     </row>
     <row r="376" spans="1:15">
-      <c r="A376" s="14" t="s">
-        <v>854</v>
-      </c>
-      <c r="B376" s="14" t="s">
-        <v>855</v>
-      </c>
-      <c r="O376" s="7" t="s">
-        <v>856</v>
-      </c>
+      <c r="A376" s="14"/>
+      <c r="B376" s="14"/>
+      <c r="O376" s="7"/>
     </row>
     <row r="377" spans="1:15">
       <c r="A377" s="14" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B377" s="14" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="O377" s="7" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
     </row>
     <row r="378" spans="1:15">
       <c r="A378" s="14" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="B378" s="14" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="O378" s="7" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
     <row r="379" spans="1:15">
       <c r="A379" s="14" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="B379" s="14" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="O379" s="7" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
     </row>
     <row r="380" spans="1:15">
       <c r="A380" s="14" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B380" s="14" t="s">
-        <v>867</v>
+        <v>851</v>
       </c>
       <c r="O380" s="7" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="381" spans="1:2">
-      <c r="A381" s="14"/>
-      <c r="B381" s="14"/>
+        <v>852</v>
+      </c>
+    </row>
+    <row r="381" spans="1:15">
+      <c r="A381" s="14" t="s">
+        <v>869</v>
+      </c>
+      <c r="B381" s="14" t="s">
+        <v>870</v>
+      </c>
+      <c r="O381" s="7" t="s">
+        <v>871</v>
+      </c>
     </row>
     <row r="382" spans="1:15">
       <c r="A382" s="14" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B382" s="14" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="O382" s="7" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
     </row>
     <row r="383" spans="1:15">
       <c r="A383" s="14" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="B383" s="14" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="O383" s="7" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
     </row>
     <row r="384" spans="1:15">
       <c r="A384" s="14" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="B384" s="14" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="O384" s="7" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
     </row>
     <row r="385" spans="1:15">
-      <c r="A385" s="14"/>
-      <c r="B385" s="14"/>
-      <c r="O385" s="7"/>
+      <c r="A385" s="14" t="s">
+        <v>881</v>
+      </c>
+      <c r="B385" s="14" t="s">
+        <v>882</v>
+      </c>
+      <c r="O385" s="7" t="s">
+        <v>883</v>
+      </c>
     </row>
     <row r="386" spans="1:15">
       <c r="A386" s="14" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="B386" s="14" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="O386" s="7" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="387" spans="1:15">
-      <c r="A387" s="14" t="s">
-        <v>880</v>
-      </c>
-      <c r="B387" s="14" t="s">
-        <v>881</v>
-      </c>
-      <c r="O387" s="7" t="s">
-        <v>882</v>
-      </c>
+        <v>886</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387" s="14"/>
+      <c r="B387" s="14"/>
     </row>
     <row r="388" spans="1:15">
       <c r="A388" s="14" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="B388" s="14" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="O388" s="7" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
     </row>
     <row r="389" spans="1:15">
       <c r="A389" s="14" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="B389" s="14" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="O389" s="7" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="390" spans="1:2">
-      <c r="A390" s="14"/>
-      <c r="B390" s="14"/>
+        <v>892</v>
+      </c>
+    </row>
+    <row r="390" spans="1:15">
+      <c r="A390" s="14" t="s">
+        <v>893</v>
+      </c>
+      <c r="B390" s="14" t="s">
+        <v>894</v>
+      </c>
+      <c r="O390" s="7" t="s">
+        <v>895</v>
+      </c>
     </row>
     <row r="391" spans="1:15">
-      <c r="A391" s="14" t="s">
-        <v>889</v>
-      </c>
-      <c r="B391" s="14" t="s">
-        <v>890</v>
-      </c>
-      <c r="O391" s="7" t="s">
-        <v>891</v>
-      </c>
+      <c r="A391" s="14"/>
+      <c r="B391" s="14"/>
+      <c r="O391" s="7"/>
     </row>
     <row r="392" spans="1:15">
       <c r="A392" s="14" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="B392" s="14" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="O392" s="7" t="s">
-        <v>894</v>
+        <v>518</v>
       </c>
     </row>
     <row r="393" spans="1:15">
       <c r="A393" s="14" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="B393" s="14" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="O393" s="7" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
     </row>
     <row r="394" spans="1:15">
-      <c r="A394" s="14"/>
-      <c r="B394" s="14"/>
-      <c r="O394" s="7"/>
+      <c r="A394" s="14" t="s">
+        <v>901</v>
+      </c>
+      <c r="B394" s="14" t="s">
+        <v>902</v>
+      </c>
+      <c r="O394" s="7" t="s">
+        <v>903</v>
+      </c>
     </row>
     <row r="395" spans="1:15">
       <c r="A395" s="14" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="B395" s="14" t="s">
-        <v>897</v>
+        <v>905</v>
       </c>
       <c r="O395" s="7" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="396" spans="1:15">
-      <c r="A396" s="14" t="s">
-        <v>899</v>
-      </c>
-      <c r="B396" s="14" t="s">
-        <v>900</v>
-      </c>
-      <c r="O396" s="7" t="s">
-        <v>901</v>
-      </c>
+        <v>906</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396" s="14"/>
+      <c r="B396" s="14"/>
     </row>
     <row r="397" spans="1:15">
       <c r="A397" s="14" t="s">
-        <v>902</v>
+        <v>907</v>
       </c>
       <c r="B397" s="14" t="s">
-        <v>903</v>
+        <v>908</v>
       </c>
       <c r="O397" s="7" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
     </row>
     <row r="398" spans="1:15">
       <c r="A398" s="14" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="B398" s="14" t="s">
-        <v>906</v>
+        <v>911</v>
       </c>
       <c r="O398" s="7" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
     </row>
     <row r="399" spans="1:15">
       <c r="A399" s="14" t="s">
-        <v>908</v>
+        <v>913</v>
       </c>
       <c r="B399" s="14" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="O399" s="7" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
     </row>
     <row r="400" spans="1:15">
-      <c r="A400" s="14" t="s">
-        <v>911</v>
-      </c>
-      <c r="B400" s="14" t="s">
-        <v>912</v>
-      </c>
-      <c r="O400" s="7" t="s">
-        <v>913</v>
-      </c>
+      <c r="A400" s="14"/>
+      <c r="B400" s="14"/>
+      <c r="O400" s="7"/>
     </row>
     <row r="401" spans="1:15">
-      <c r="A401" s="14"/>
-      <c r="B401" s="14"/>
+      <c r="A401" s="14" t="s">
+        <v>914</v>
+      </c>
+      <c r="B401" s="14" t="s">
+        <v>915</v>
+      </c>
       <c r="O401" s="7" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
     </row>
     <row r="402" spans="1:15">
       <c r="A402" s="14" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="B402" s="14" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="O402" s="7" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
     </row>
     <row r="403" spans="1:15">
       <c r="A403" s="14" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="B403" s="14" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="O403" s="7" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
     </row>
     <row r="404" spans="1:15">
       <c r="A404" s="14" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="B404" s="14" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="O404" s="7" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
     </row>
     <row r="405" spans="1:15">
-      <c r="A405" s="14"/>
-      <c r="B405" s="14"/>
-      <c r="O405" s="7"/>
+      <c r="A405" s="14" t="s">
+        <v>926</v>
+      </c>
+      <c r="B405" s="14" t="s">
+        <v>927</v>
+      </c>
+      <c r="O405" s="7" t="s">
+        <v>928</v>
+      </c>
     </row>
     <row r="406" spans="1:15">
       <c r="A406" s="14" t="s">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="B406" s="14" t="s">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="O406" s="7" t="s">
-        <v>925</v>
+        <v>931</v>
       </c>
     </row>
     <row r="407" spans="1:15">
-      <c r="A407" s="14" t="s">
-        <v>926</v>
-      </c>
-      <c r="B407" s="14" t="s">
-        <v>927</v>
-      </c>
+      <c r="A407" s="14"/>
+      <c r="B407" s="14"/>
       <c r="O407" s="7" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
     </row>
     <row r="408" spans="1:15">
       <c r="A408" s="14" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="B408" s="14" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="O408" s="7" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
     </row>
     <row r="409" spans="1:15">
       <c r="A409" s="14" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B409" s="14" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="O409" s="7" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
     </row>
     <row r="410" spans="1:15">
       <c r="A410" s="14" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="B410" s="14" t="s">
-        <v>887</v>
+        <v>939</v>
       </c>
       <c r="O410" s="7" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
     </row>
     <row r="411" spans="1:15">
-      <c r="A411" s="14" t="s">
-        <v>937</v>
-      </c>
-      <c r="B411" s="14" t="s">
-        <v>938</v>
-      </c>
-      <c r="O411" s="7" t="s">
-        <v>939</v>
+      <c r="A411" s="14"/>
+      <c r="B411" s="14"/>
+      <c r="O411" s="7"/>
+    </row>
+    <row r="412" spans="1:15">
+      <c r="A412" s="14" t="s">
+        <v>941</v>
+      </c>
+      <c r="B412" s="14" t="s">
+        <v>942</v>
+      </c>
+      <c r="O412" s="7" t="s">
+        <v>943</v>
       </c>
     </row>
     <row r="413" spans="1:15">
       <c r="A413" s="14" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="B413" s="14" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="O413" s="7" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
     </row>
     <row r="414" spans="1:15">
       <c r="A414" s="14" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="B414" s="14" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="O414" s="7" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
     </row>
     <row r="415" spans="1:15">
       <c r="A415" s="14" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B415" s="14" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="O415" s="7" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
     </row>
     <row r="416" spans="1:15">
-      <c r="A416" s="14"/>
-      <c r="B416" s="14"/>
-      <c r="O416" s="7"/>
+      <c r="A416" s="14" t="s">
+        <v>953</v>
+      </c>
+      <c r="B416" s="14" t="s">
+        <v>905</v>
+      </c>
+      <c r="O416" s="7" t="s">
+        <v>954</v>
+      </c>
     </row>
     <row r="417" spans="1:15">
       <c r="A417" s="14" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="B417" s="14" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="O417" s="7" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="418" spans="1:15">
-      <c r="A418" s="14" t="s">
-        <v>952</v>
-      </c>
-      <c r="B418" s="14" t="s">
-        <v>953</v>
-      </c>
-      <c r="O418" s="7" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
     </row>
     <row r="419" spans="1:15">
       <c r="A419" s="14" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="B419" s="14" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="O419" s="7" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
     </row>
     <row r="420" spans="1:15">
       <c r="A420" s="14" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="B420" s="14" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="O420" s="7" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
     </row>
     <row r="421" spans="1:15">
       <c r="A421" s="14" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="B421" s="14" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="O421" s="7" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
     </row>
     <row r="422" spans="1:15">
-      <c r="A422" s="14" t="s">
-        <v>964</v>
-      </c>
-      <c r="B422" s="14" t="s">
-        <v>965</v>
-      </c>
-      <c r="O422" s="7" t="s">
-        <v>966</v>
-      </c>
+      <c r="A422" s="14"/>
+      <c r="B422" s="14"/>
+      <c r="O422" s="7"/>
     </row>
     <row r="423" spans="1:15">
       <c r="A423" s="14" t="s">
@@ -12558,113 +12630,113 @@
         <v>975</v>
       </c>
     </row>
-    <row r="426" spans="1:2">
-      <c r="A426" s="14"/>
-      <c r="B426" s="14"/>
+    <row r="426" spans="1:15">
+      <c r="A426" s="14" t="s">
+        <v>976</v>
+      </c>
+      <c r="B426" s="14" t="s">
+        <v>977</v>
+      </c>
+      <c r="O426" s="7" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="427" spans="1:15">
       <c r="A427" s="14" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="B427" s="14" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="O427" s="7" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
     </row>
     <row r="428" spans="1:15">
       <c r="A428" s="14" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="B428" s="14" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="O428" s="7" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
     </row>
     <row r="429" spans="1:15">
       <c r="A429" s="14" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="B429" s="14" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="O429" s="7" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
     </row>
     <row r="430" spans="1:15">
-      <c r="A430" s="14"/>
-      <c r="B430" s="14"/>
-      <c r="O430" s="7"/>
+      <c r="A430" s="14" t="s">
+        <v>988</v>
+      </c>
+      <c r="B430" s="14" t="s">
+        <v>989</v>
+      </c>
+      <c r="O430" s="7" t="s">
+        <v>990</v>
+      </c>
     </row>
     <row r="431" spans="1:15">
       <c r="A431" s="14" t="s">
-        <v>985</v>
+        <v>991</v>
       </c>
       <c r="B431" s="14" t="s">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="O431" s="7" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="432" spans="1:15">
-      <c r="A432" s="14" t="s">
-        <v>988</v>
-      </c>
-      <c r="B432" s="14" t="s">
-        <v>989</v>
-      </c>
-      <c r="O432" s="7" t="s">
-        <v>990</v>
-      </c>
+        <v>993</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432" s="14"/>
+      <c r="B432" s="14"/>
     </row>
     <row r="433" spans="1:15">
       <c r="A433" s="14" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="B433" s="14" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="O433" s="7" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
     </row>
     <row r="434" spans="1:15">
       <c r="A434" s="14" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="B434" s="14" t="s">
-        <v>995</v>
-      </c>
-      <c r="O434" s="2" t="s">
-        <v>996</v>
+        <v>998</v>
+      </c>
+      <c r="O434" s="7" t="s">
+        <v>999</v>
       </c>
     </row>
     <row r="435" spans="1:15">
       <c r="A435" s="14" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="B435" s="14" t="s">
-        <v>998</v>
-      </c>
-      <c r="O435" s="2" t="s">
-        <v>999</v>
+        <v>1001</v>
+      </c>
+      <c r="O435" s="7" t="s">
+        <v>1002</v>
       </c>
     </row>
     <row r="436" spans="1:15">
-      <c r="A436" s="14" t="s">
-        <v>1000</v>
-      </c>
-      <c r="B436" s="14" t="s">
-        <v>1001</v>
-      </c>
-      <c r="O436" s="2" t="s">
-        <v>1002</v>
-      </c>
+      <c r="A436" s="14"/>
+      <c r="B436" s="14"/>
+      <c r="O436" s="7"/>
     </row>
     <row r="437" spans="1:15">
       <c r="A437" s="14" t="s">
@@ -12673,7 +12745,7 @@
       <c r="B437" s="14" t="s">
         <v>1004</v>
       </c>
-      <c r="O437" s="2" t="s">
+      <c r="O437" s="7" t="s">
         <v>1005</v>
       </c>
     </row>
@@ -12684,544 +12756,544 @@
       <c r="B438" s="14" t="s">
         <v>1007</v>
       </c>
-      <c r="O438" s="2" t="s">
+      <c r="O438" s="7" t="s">
         <v>1008</v>
       </c>
     </row>
-    <row r="439" spans="1:2">
-      <c r="A439" s="14"/>
-      <c r="B439" s="14"/>
+    <row r="439" spans="1:15">
+      <c r="A439" s="14" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B439" s="14" t="s">
+        <v>1010</v>
+      </c>
+      <c r="O439" s="7" t="s">
+        <v>1011</v>
+      </c>
     </row>
     <row r="440" spans="1:15">
       <c r="A440" s="14" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="B440" s="14" t="s">
-        <v>1010</v>
-      </c>
-      <c r="O440" s="7" t="s">
-        <v>1011</v>
+        <v>1013</v>
+      </c>
+      <c r="O440" s="2" t="s">
+        <v>1014</v>
       </c>
     </row>
     <row r="441" spans="1:15">
       <c r="A441" s="14" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="B441" s="14" t="s">
-        <v>1013</v>
-      </c>
-      <c r="O441" s="7" t="s">
-        <v>1014</v>
+        <v>1016</v>
+      </c>
+      <c r="O441" s="2" t="s">
+        <v>1017</v>
       </c>
     </row>
     <row r="442" spans="1:15">
       <c r="A442" s="14" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="B442" s="14" t="s">
-        <v>1016</v>
-      </c>
-      <c r="O442" s="7" t="s">
-        <v>1017</v>
+        <v>1019</v>
+      </c>
+      <c r="O442" s="2" t="s">
+        <v>1020</v>
       </c>
     </row>
     <row r="443" spans="1:15">
-      <c r="A443" s="14"/>
-      <c r="B443" s="14"/>
-      <c r="O443" s="7"/>
+      <c r="A443" s="14" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B443" s="14" t="s">
+        <v>1022</v>
+      </c>
+      <c r="O443" s="2" t="s">
+        <v>1023</v>
+      </c>
     </row>
     <row r="444" spans="1:15">
       <c r="A444" s="14" t="s">
-        <v>1018</v>
+        <v>1024</v>
       </c>
       <c r="B444" s="14" t="s">
-        <v>1019</v>
-      </c>
-      <c r="O444" s="7" t="s">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="445" spans="1:15">
-      <c r="A445" s="14" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B445" s="14" t="s">
-        <v>1022</v>
-      </c>
-      <c r="O445" s="7" t="s">
-        <v>1023</v>
-      </c>
+        <v>1025</v>
+      </c>
+      <c r="O444" s="2" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445" s="14"/>
+      <c r="B445" s="14"/>
     </row>
     <row r="446" spans="1:15">
       <c r="A446" s="14" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="B446" s="14" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="O446" s="7" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="447" spans="1:15">
       <c r="A447" s="14" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="B447" s="14" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="O447" s="7" t="s">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="448" spans="1:2">
-      <c r="A448" s="14"/>
-      <c r="B448" s="14"/>
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="448" spans="1:15">
+      <c r="A448" s="14" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B448" s="14" t="s">
+        <v>1034</v>
+      </c>
+      <c r="O448" s="7" t="s">
+        <v>1035</v>
+      </c>
     </row>
     <row r="449" spans="1:15">
-      <c r="A449" s="14" t="s">
-        <v>1030</v>
-      </c>
-      <c r="B449" s="14" t="s">
-        <v>1031</v>
-      </c>
-      <c r="O449" s="7" t="s">
-        <v>1032</v>
-      </c>
+      <c r="A449" s="14"/>
+      <c r="B449" s="14"/>
+      <c r="O449" s="7"/>
     </row>
     <row r="450" spans="1:15">
       <c r="A450" s="14" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="B450" s="14" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="O450" s="7" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="451" spans="1:15">
       <c r="A451" s="14" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="B451" s="14" t="s">
-        <v>1034</v>
+        <v>1040</v>
       </c>
       <c r="O451" s="7" t="s">
-        <v>1035</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="452" spans="1:15">
-      <c r="A452" s="14"/>
-      <c r="B452" s="14"/>
-      <c r="O452" s="7"/>
+      <c r="A452" s="14" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B452" s="14" t="s">
+        <v>1043</v>
+      </c>
+      <c r="O452" s="7" t="s">
+        <v>1044</v>
+      </c>
     </row>
     <row r="453" spans="1:15">
       <c r="A453" s="14" t="s">
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="B453" s="14" t="s">
-        <v>1038</v>
+        <v>1046</v>
       </c>
       <c r="O453" s="7" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="454" spans="1:15">
-      <c r="A454" s="14" t="s">
-        <v>1040</v>
-      </c>
-      <c r="B454" s="14" t="s">
-        <v>1041</v>
-      </c>
-      <c r="O454" s="7" t="s">
-        <v>1042</v>
-      </c>
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454" s="14"/>
+      <c r="B454" s="14"/>
     </row>
     <row r="455" spans="1:15">
       <c r="A455" s="14" t="s">
-        <v>1043</v>
+        <v>1048</v>
       </c>
       <c r="B455" s="14" t="s">
-        <v>1044</v>
+        <v>1049</v>
       </c>
       <c r="O455" s="7" t="s">
-        <v>1045</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="456" spans="1:15">
       <c r="A456" s="14" t="s">
-        <v>1046</v>
+        <v>1051</v>
       </c>
       <c r="B456" s="14" t="s">
-        <v>1047</v>
+        <v>1052</v>
       </c>
       <c r="O456" s="7" t="s">
-        <v>1048</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="457" spans="1:15">
       <c r="A457" s="14" t="s">
-        <v>1049</v>
+        <v>1054</v>
       </c>
       <c r="B457" s="14" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="O457" s="7" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="458" spans="1:2">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="458" spans="1:15">
       <c r="A458" s="14"/>
       <c r="B458" s="14"/>
+      <c r="O458" s="7"/>
     </row>
     <row r="459" spans="1:15">
       <c r="A459" s="14" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="B459" s="14" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="O459" s="7" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="460" spans="1:15">
       <c r="A460" s="14" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="B460" s="14" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="O460" s="7" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="461" spans="1:15">
       <c r="A461" s="14" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="B461" s="14" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="O461" s="7" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="462" spans="1:15">
-      <c r="A462" s="14"/>
-      <c r="B462" s="14"/>
-      <c r="O462" s="7"/>
+      <c r="A462" s="14" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B462" s="14" t="s">
+        <v>1065</v>
+      </c>
+      <c r="O462" s="7" t="s">
+        <v>1066</v>
+      </c>
     </row>
     <row r="463" spans="1:15">
       <c r="A463" s="14" t="s">
-        <v>1059</v>
+        <v>1067</v>
       </c>
       <c r="B463" s="14" t="s">
-        <v>1060</v>
+        <v>1068</v>
       </c>
       <c r="O463" s="7" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="464" spans="1:15">
-      <c r="A464" s="14" t="s">
-        <v>1062</v>
-      </c>
-      <c r="B464" s="14" t="s">
-        <v>1063</v>
-      </c>
-      <c r="O464" s="7" t="s">
-        <v>1064</v>
-      </c>
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464" s="14"/>
+      <c r="B464" s="14"/>
     </row>
     <row r="465" spans="1:15">
       <c r="A465" s="14" t="s">
-        <v>1065</v>
+        <v>1070</v>
       </c>
       <c r="B465" s="14" t="s">
-        <v>1066</v>
+        <v>1071</v>
       </c>
       <c r="O465" s="7" t="s">
-        <v>1067</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="466" spans="1:15">
       <c r="A466" s="14" t="s">
-        <v>1068</v>
+        <v>1073</v>
       </c>
       <c r="B466" s="14" t="s">
-        <v>1069</v>
+        <v>1074</v>
       </c>
       <c r="O466" s="7" t="s">
-        <v>1070</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="467" spans="1:15">
       <c r="A467" s="14" t="s">
-        <v>1071</v>
+        <v>1076</v>
       </c>
       <c r="B467" s="14" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="O467" s="7" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="468" spans="1:15">
-      <c r="A468" s="14" t="s">
-        <v>1074</v>
-      </c>
-      <c r="B468" s="14" t="s">
-        <v>1075</v>
-      </c>
-      <c r="O468" s="7" t="s">
-        <v>1076</v>
-      </c>
+      <c r="A468" s="14"/>
+      <c r="B468" s="14"/>
+      <c r="O468" s="7"/>
     </row>
     <row r="469" spans="1:15">
       <c r="A469" s="14" t="s">
         <v>1077</v>
       </c>
       <c r="B469" s="14" t="s">
-        <v>887</v>
+        <v>1078</v>
       </c>
       <c r="O469" s="7" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="470" spans="1:15">
       <c r="A470" s="14" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B470" s="14" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="O470" s="7" t="s">
-        <v>1081</v>
-      </c>
-    </row>
-    <row r="471" spans="1:2">
-      <c r="A471" s="14"/>
-      <c r="B471" s="14"/>
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="471" spans="1:15">
+      <c r="A471" s="14" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B471" s="14" t="s">
+        <v>1084</v>
+      </c>
+      <c r="O471" s="7" t="s">
+        <v>1085</v>
+      </c>
     </row>
     <row r="472" spans="1:15">
       <c r="A472" s="14" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="B472" s="14" t="s">
-        <v>121</v>
+        <v>1087</v>
       </c>
       <c r="O472" s="7" t="s">
-        <v>1083</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="473" spans="1:15">
       <c r="A473" s="14" t="s">
-        <v>1084</v>
+        <v>1089</v>
       </c>
       <c r="B473" s="14" t="s">
-        <v>1085</v>
+        <v>1090</v>
       </c>
       <c r="O473" s="7" t="s">
-        <v>1086</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="474" spans="1:15">
       <c r="A474" s="14" t="s">
-        <v>1087</v>
+        <v>1092</v>
       </c>
       <c r="B474" s="14" t="s">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="O474" s="7" t="s">
-        <v>1089</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="475" spans="1:15">
-      <c r="A475" s="14"/>
-      <c r="B475" s="14"/>
-      <c r="O475" s="7"/>
+      <c r="A475" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B475" s="14" t="s">
+        <v>905</v>
+      </c>
+      <c r="O475" s="7" t="s">
+        <v>1096</v>
+      </c>
     </row>
     <row r="476" spans="1:15">
       <c r="A476" s="14" t="s">
-        <v>1090</v>
+        <v>1097</v>
       </c>
       <c r="B476" s="14" t="s">
-        <v>1091</v>
+        <v>1098</v>
       </c>
       <c r="O476" s="7" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="477" spans="1:15">
-      <c r="A477" s="14" t="s">
-        <v>1093</v>
-      </c>
-      <c r="B477" s="14" t="s">
-        <v>1094</v>
-      </c>
-      <c r="O477" s="7" t="s">
-        <v>1095</v>
-      </c>
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477" s="14"/>
+      <c r="B477" s="14"/>
     </row>
     <row r="478" spans="1:15">
       <c r="A478" s="14" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="B478" s="14" t="s">
-        <v>1097</v>
+        <v>121</v>
       </c>
       <c r="O478" s="7" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="479" spans="1:15">
       <c r="A479" s="14" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="B479" s="14" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="O479" s="7" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="480" spans="1:2">
-      <c r="A480" s="14"/>
-      <c r="B480" s="14"/>
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="480" spans="1:15">
+      <c r="A480" s="14" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B480" s="14" t="s">
+        <v>1106</v>
+      </c>
+      <c r="O480" s="7" t="s">
+        <v>1107</v>
+      </c>
     </row>
     <row r="481" spans="1:15">
-      <c r="A481" s="14" t="s">
-        <v>1102</v>
-      </c>
-      <c r="B481" s="14" t="s">
-        <v>1103</v>
-      </c>
-      <c r="O481" s="2" t="s">
-        <v>1104</v>
-      </c>
+      <c r="A481" s="14"/>
+      <c r="B481" s="14"/>
+      <c r="O481" s="7"/>
     </row>
     <row r="482" spans="1:15">
       <c r="A482" s="14" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="B482" s="14" t="s">
-        <v>1106</v>
-      </c>
-      <c r="O482" s="2" t="s">
-        <v>1107</v>
+        <v>1109</v>
+      </c>
+      <c r="O482" s="7" t="s">
+        <v>1110</v>
       </c>
     </row>
     <row r="483" spans="1:15">
       <c r="A483" s="14" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="B483" s="14" t="s">
-        <v>1109</v>
-      </c>
-      <c r="O483" s="2" t="s">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="484" spans="1:2">
-      <c r="A484" s="14"/>
-      <c r="B484" s="14"/>
+        <v>1112</v>
+      </c>
+      <c r="O483" s="7" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="484" spans="1:15">
+      <c r="A484" s="14" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B484" s="14" t="s">
+        <v>1115</v>
+      </c>
+      <c r="O484" s="7" t="s">
+        <v>1116</v>
+      </c>
     </row>
     <row r="485" spans="1:15">
       <c r="A485" s="14" t="s">
-        <v>1111</v>
+        <v>1117</v>
       </c>
       <c r="B485" s="14" t="s">
-        <v>1112</v>
-      </c>
-      <c r="O485" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="486" spans="1:15">
-      <c r="A486" s="14" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B486" s="14" t="s">
-        <v>1115</v>
-      </c>
-      <c r="O486" s="2" t="s">
-        <v>1116</v>
-      </c>
+        <v>1118</v>
+      </c>
+      <c r="O485" s="7" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486" s="14"/>
+      <c r="B486" s="14"/>
     </row>
     <row r="487" spans="1:15">
       <c r="A487" s="14" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="B487" s="14" t="s">
-        <v>887</v>
+        <v>1121</v>
       </c>
       <c r="O487" s="2" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="488" spans="1:15">
       <c r="A488" s="14" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="B488" s="14" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="O488" s="2" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="489" spans="1:15">
       <c r="A489" s="14" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="B489" s="14" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="O489" s="2" t="s">
-        <v>1124</v>
-      </c>
-    </row>
-    <row r="490" spans="1:15">
-      <c r="A490" s="14" t="s">
-        <v>1125</v>
-      </c>
-      <c r="B490" s="14" t="s">
-        <v>1126</v>
-      </c>
-      <c r="O490" s="2" t="s">
-        <v>1127</v>
-      </c>
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2">
+      <c r="A490" s="14"/>
+      <c r="B490" s="14"/>
     </row>
     <row r="491" spans="1:15">
       <c r="A491" s="14" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B491" s="14" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="O491" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="492" spans="1:15">
       <c r="A492" s="14" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B492" s="14" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="O492" s="2" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="493" spans="1:15">
       <c r="A493" s="14" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B493" s="14" t="s">
-        <v>1135</v>
+        <v>905</v>
       </c>
       <c r="O493" s="2" t="s">
         <v>1136</v>
@@ -13238,71 +13310,85 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="495" spans="1:2">
-      <c r="A495" s="14"/>
-      <c r="B495" s="14"/>
+    <row r="495" spans="1:15">
+      <c r="A495" s="14" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B495" s="14" t="s">
+        <v>1141</v>
+      </c>
+      <c r="O495" s="2" t="s">
+        <v>1142</v>
+      </c>
     </row>
     <row r="496" spans="1:15">
       <c r="A496" s="14" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="B496" s="14" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="O496" s="2" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="497" spans="1:2">
-      <c r="A497" s="14"/>
-      <c r="B497" s="14"/>
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="497" spans="1:15">
+      <c r="A497" s="14" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B497" s="14" t="s">
+        <v>1147</v>
+      </c>
+      <c r="O497" s="2" t="s">
+        <v>1148</v>
+      </c>
     </row>
     <row r="498" spans="1:15">
       <c r="A498" s="14" t="s">
-        <v>1143</v>
+        <v>1149</v>
       </c>
       <c r="B498" s="14" t="s">
-        <v>1144</v>
+        <v>1150</v>
       </c>
       <c r="O498" s="2" t="s">
-        <v>1145</v>
-      </c>
-    </row>
-    <row r="499" spans="1:2">
-      <c r="A499" s="14"/>
-      <c r="B499" s="14"/>
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="499" spans="1:15">
+      <c r="A499" s="14" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B499" s="14" t="s">
+        <v>1153</v>
+      </c>
+      <c r="O499" s="2" t="s">
+        <v>1154</v>
+      </c>
     </row>
     <row r="500" spans="1:15">
       <c r="A500" s="14" t="s">
-        <v>1146</v>
+        <v>1155</v>
       </c>
       <c r="B500" s="14" t="s">
-        <v>1147</v>
-      </c>
-      <c r="O500" s="7" t="s">
-        <v>1148</v>
-      </c>
-    </row>
-    <row r="501" spans="1:15">
-      <c r="A501" s="14" t="s">
-        <v>1149</v>
-      </c>
-      <c r="B501" s="14" t="s">
-        <v>1150</v>
-      </c>
-      <c r="O501" s="7" t="s">
-        <v>1151</v>
-      </c>
+        <v>1156</v>
+      </c>
+      <c r="O500" s="2" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2">
+      <c r="A501" s="14"/>
+      <c r="B501" s="14"/>
     </row>
     <row r="502" spans="1:15">
       <c r="A502" s="14" t="s">
-        <v>1152</v>
+        <v>1158</v>
       </c>
       <c r="B502" s="14" t="s">
-        <v>1150</v>
-      </c>
-      <c r="O502" s="7" t="s">
-        <v>1153</v>
+        <v>1159</v>
+      </c>
+      <c r="O502" s="2" t="s">
+        <v>1160</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -13311,76 +13397,76 @@
     </row>
     <row r="504" spans="1:15">
       <c r="A504" s="14" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="B504" s="14" t="s">
-        <v>1155</v>
-      </c>
-      <c r="O504" s="7" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="505" spans="1:15">
-      <c r="A505" s="14" t="s">
-        <v>1157</v>
-      </c>
-      <c r="B505" s="14" t="s">
-        <v>1158</v>
-      </c>
-      <c r="O505" s="7" t="s">
-        <v>1159</v>
-      </c>
-    </row>
-    <row r="506" spans="1:2">
-      <c r="A506" s="14"/>
-      <c r="B506" s="14"/>
+        <v>1162</v>
+      </c>
+      <c r="O504" s="2" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2">
+      <c r="A505" s="14"/>
+      <c r="B505" s="14"/>
+    </row>
+    <row r="506" spans="1:15">
+      <c r="A506" s="14" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B506" s="14" t="s">
+        <v>1165</v>
+      </c>
+      <c r="O506" s="7" t="s">
+        <v>1166</v>
+      </c>
     </row>
     <row r="507" spans="1:15">
       <c r="A507" s="14" t="s">
-        <v>1160</v>
+        <v>1167</v>
       </c>
       <c r="B507" s="14" t="s">
-        <v>1161</v>
+        <v>1168</v>
       </c>
       <c r="O507" s="7" t="s">
-        <v>1162</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="508" spans="1:15">
       <c r="A508" s="14" t="s">
-        <v>1163</v>
+        <v>1170</v>
       </c>
       <c r="B508" s="14" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="O508" s="7" t="s">
-        <v>1165</v>
-      </c>
-    </row>
-    <row r="509" spans="1:15">
-      <c r="A509" s="14" t="s">
-        <v>1166</v>
-      </c>
-      <c r="B509" s="14" t="s">
-        <v>1164</v>
-      </c>
-      <c r="O509" s="7" t="s">
-        <v>1167</v>
-      </c>
-    </row>
-    <row r="510" spans="1:2">
-      <c r="A510" s="14"/>
-      <c r="B510" s="14"/>
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2">
+      <c r="A509" s="14"/>
+      <c r="B509" s="14"/>
+    </row>
+    <row r="510" spans="1:15">
+      <c r="A510" s="14" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B510" s="14" t="s">
+        <v>1173</v>
+      </c>
+      <c r="O510" s="7" t="s">
+        <v>1174</v>
+      </c>
     </row>
     <row r="511" spans="1:15">
       <c r="A511" s="14" t="s">
-        <v>1168</v>
+        <v>1175</v>
       </c>
       <c r="B511" s="14" t="s">
-        <v>1169</v>
-      </c>
-      <c r="O511" s="2" t="s">
-        <v>1170</v>
+        <v>1176</v>
+      </c>
+      <c r="O511" s="7" t="s">
+        <v>1177</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -13389,35 +13475,35 @@
     </row>
     <row r="513" spans="1:15">
       <c r="A513" s="14" t="s">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="B513" s="14" t="s">
-        <v>1172</v>
-      </c>
-      <c r="O513" s="2" t="s">
-        <v>1173</v>
+        <v>1179</v>
+      </c>
+      <c r="O513" s="7" t="s">
+        <v>1180</v>
       </c>
     </row>
     <row r="514" spans="1:15">
       <c r="A514" s="14" t="s">
-        <v>1174</v>
+        <v>1181</v>
       </c>
       <c r="B514" s="14" t="s">
-        <v>1175</v>
-      </c>
-      <c r="O514" s="2" t="s">
-        <v>1176</v>
+        <v>1182</v>
+      </c>
+      <c r="O514" s="7" t="s">
+        <v>1183</v>
       </c>
     </row>
     <row r="515" spans="1:15">
       <c r="A515" s="14" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="B515" s="14" t="s">
-        <v>1175</v>
-      </c>
-      <c r="O515" s="2" t="s">
-        <v>1176</v>
+        <v>1182</v>
+      </c>
+      <c r="O515" s="7" t="s">
+        <v>1185</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -13426,971 +13512,957 @@
     </row>
     <row r="517" spans="1:15">
       <c r="A517" s="14" t="s">
-        <v>1178</v>
+        <v>1186</v>
       </c>
       <c r="B517" s="14" t="s">
-        <v>1179</v>
-      </c>
-      <c r="O517" s="7" t="s">
-        <v>1180</v>
-      </c>
-    </row>
-    <row r="518" spans="1:15">
-      <c r="A518" s="14" t="s">
-        <v>1181</v>
-      </c>
-      <c r="B518" s="14" t="s">
-        <v>1182</v>
-      </c>
-      <c r="O518" s="7" t="s">
-        <v>1183</v>
-      </c>
+        <v>1187</v>
+      </c>
+      <c r="O517" s="2" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518" s="14"/>
+      <c r="B518" s="14"/>
     </row>
     <row r="519" spans="1:15">
       <c r="A519" s="14" t="s">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="B519" s="14" t="s">
-        <v>1182</v>
-      </c>
-      <c r="O519" s="7" t="s">
-        <v>1183</v>
+        <v>1190</v>
+      </c>
+      <c r="O519" s="2" t="s">
+        <v>1191</v>
       </c>
     </row>
     <row r="520" spans="1:15">
-      <c r="A520" s="14"/>
-      <c r="B520" s="14"/>
-      <c r="O520" s="7"/>
+      <c r="A520" s="14" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B520" s="14" t="s">
+        <v>1193</v>
+      </c>
+      <c r="O520" s="2" t="s">
+        <v>1194</v>
+      </c>
     </row>
     <row r="521" spans="1:15">
       <c r="A521" s="14" t="s">
-        <v>1185</v>
+        <v>1195</v>
       </c>
       <c r="B521" s="14" t="s">
-        <v>1186</v>
+        <v>1193</v>
       </c>
       <c r="O521" s="2" t="s">
-        <v>1187</v>
-      </c>
-    </row>
-    <row r="522" spans="1:15">
-      <c r="A522" s="14" t="s">
-        <v>1188</v>
-      </c>
-      <c r="B522" s="14" t="s">
-        <v>1189</v>
-      </c>
-      <c r="O522" s="2" t="s">
-        <v>1190</v>
-      </c>
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2">
+      <c r="A522" s="14"/>
+      <c r="B522" s="14"/>
     </row>
     <row r="523" spans="1:15">
       <c r="A523" s="14" t="s">
-        <v>1191</v>
+        <v>1196</v>
       </c>
       <c r="B523" s="14" t="s">
-        <v>1192</v>
-      </c>
-      <c r="O523" s="2" t="s">
-        <v>1193</v>
+        <v>1197</v>
+      </c>
+      <c r="O523" s="7" t="s">
+        <v>1198</v>
       </c>
     </row>
     <row r="524" spans="1:15">
       <c r="A524" s="14" t="s">
-        <v>1194</v>
+        <v>1199</v>
       </c>
       <c r="B524" s="14" t="s">
-        <v>1195</v>
+        <v>1200</v>
       </c>
       <c r="O524" s="7" t="s">
-        <v>1196</v>
-      </c>
-    </row>
-    <row r="525" spans="1:2">
-      <c r="A525" s="14"/>
-      <c r="B525" s="14"/>
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="525" spans="1:15">
+      <c r="A525" s="14" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B525" s="14" t="s">
+        <v>1200</v>
+      </c>
+      <c r="O525" s="7" t="s">
+        <v>1201</v>
+      </c>
     </row>
     <row r="526" spans="1:15">
-      <c r="A526" s="14" t="s">
-        <v>1197</v>
-      </c>
-      <c r="B526" s="14" t="s">
-        <v>1198</v>
-      </c>
-      <c r="O526" s="7" t="s">
-        <v>1199</v>
-      </c>
+      <c r="A526" s="14"/>
+      <c r="B526" s="14"/>
+      <c r="O526" s="7"/>
     </row>
     <row r="527" spans="1:15">
       <c r="A527" s="14" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="B527" s="14" t="s">
-        <v>1201</v>
-      </c>
-      <c r="O527" s="7" t="s">
-        <v>1202</v>
-      </c>
-    </row>
-    <row r="528" ht="18.75" spans="1:15">
+        <v>1204</v>
+      </c>
+      <c r="O527" s="2" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="528" spans="1:15">
       <c r="A528" s="14" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="B528" s="14" t="s">
-        <v>1201</v>
-      </c>
-      <c r="O528" s="7" t="s">
-        <v>1204</v>
-      </c>
-    </row>
-    <row r="529" spans="1:2">
-      <c r="A529" s="14"/>
-      <c r="B529" s="14"/>
+        <v>1207</v>
+      </c>
+      <c r="O528" s="2" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="529" spans="1:15">
+      <c r="A529" s="14" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B529" s="14" t="s">
+        <v>1210</v>
+      </c>
+      <c r="O529" s="2" t="s">
+        <v>1211</v>
+      </c>
     </row>
     <row r="530" spans="1:15">
       <c r="A530" s="14" t="s">
-        <v>1205</v>
+        <v>1212</v>
       </c>
       <c r="B530" s="14" t="s">
-        <v>1206</v>
+        <v>1213</v>
       </c>
       <c r="O530" s="7" t="s">
-        <v>1207</v>
-      </c>
-    </row>
-    <row r="531" spans="1:15">
-      <c r="A531" s="14" t="s">
-        <v>1208</v>
-      </c>
-      <c r="B531" s="14" t="s">
-        <v>1209</v>
-      </c>
-      <c r="O531" s="7" t="s">
-        <v>1210</v>
-      </c>
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531" s="14"/>
+      <c r="B531" s="14"/>
     </row>
     <row r="532" spans="1:15">
       <c r="A532" s="14" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="B532" s="14" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="O532" s="7" t="s">
-        <v>1213</v>
-      </c>
-    </row>
-    <row r="533" spans="1:2">
-      <c r="A533" s="14"/>
-      <c r="B533" s="14"/>
-    </row>
-    <row r="534" spans="1:15">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="533" spans="1:15">
+      <c r="A533" s="14" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B533" s="14" t="s">
+        <v>1219</v>
+      </c>
+      <c r="O533" s="7" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="534" ht="18.75" spans="1:15">
       <c r="A534" s="14" t="s">
-        <v>1214</v>
+        <v>1221</v>
       </c>
       <c r="B534" s="14" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="O534" s="7" t="s">
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="535" spans="1:15">
-      <c r="A535" s="14" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B535" s="14" t="s">
-        <v>1218</v>
-      </c>
-      <c r="O535" s="7" t="s">
-        <v>1219</v>
-      </c>
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535" s="14"/>
+      <c r="B535" s="14"/>
     </row>
     <row r="536" spans="1:15">
       <c r="A536" s="14" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="B536" s="14" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="O536" s="7" t="s">
-        <v>1219</v>
-      </c>
-    </row>
-    <row r="537" spans="1:2">
-      <c r="A537" s="14"/>
-      <c r="B537" s="14"/>
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="537" spans="1:15">
+      <c r="A537" s="14" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B537" s="14" t="s">
+        <v>1227</v>
+      </c>
+      <c r="O537" s="7" t="s">
+        <v>1228</v>
+      </c>
     </row>
     <row r="538" spans="1:15">
       <c r="A538" s="14" t="s">
-        <v>1222</v>
+        <v>1229</v>
       </c>
       <c r="B538" s="14" t="s">
-        <v>1223</v>
+        <v>1230</v>
       </c>
       <c r="O538" s="7" t="s">
-        <v>1224</v>
-      </c>
-    </row>
-    <row r="539" spans="1:15">
-      <c r="A539" s="14" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B539" s="14" t="s">
-        <v>1226</v>
-      </c>
-      <c r="O539" s="7" t="s">
-        <v>1227</v>
-      </c>
-    </row>
-    <row r="540" spans="1:2">
-      <c r="A540" s="14"/>
-      <c r="B540" s="14"/>
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539" s="14"/>
+      <c r="B539" s="14"/>
+    </row>
+    <row r="540" spans="1:15">
+      <c r="A540" s="14" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B540" s="14" t="s">
+        <v>1233</v>
+      </c>
+      <c r="O540" s="7" t="s">
+        <v>1234</v>
+      </c>
     </row>
     <row r="541" spans="1:15">
       <c r="A541" s="14" t="s">
-        <v>1228</v>
+        <v>1235</v>
       </c>
       <c r="B541" s="14" t="s">
-        <v>1229</v>
+        <v>1236</v>
       </c>
       <c r="O541" s="7" t="s">
-        <v>1230</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="542" spans="1:15">
       <c r="A542" s="14" t="s">
-        <v>1231</v>
+        <v>1238</v>
       </c>
       <c r="B542" s="14" t="s">
-        <v>1232</v>
+        <v>1239</v>
       </c>
       <c r="O542" s="7" t="s">
-        <v>1233</v>
-      </c>
-    </row>
-    <row r="543" spans="1:15">
-      <c r="A543" s="14" t="s">
-        <v>1234</v>
-      </c>
-      <c r="B543" s="14" t="s">
-        <v>1235</v>
-      </c>
-      <c r="O543" s="7" t="s">
-        <v>1236</v>
-      </c>
-    </row>
-    <row r="544" spans="1:2">
-      <c r="A544" s="14"/>
-      <c r="B544" s="14"/>
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543" s="14"/>
+      <c r="B543" s="14"/>
+    </row>
+    <row r="544" spans="1:15">
+      <c r="A544" s="14" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B544" s="14" t="s">
+        <v>1241</v>
+      </c>
+      <c r="O544" s="7" t="s">
+        <v>1242</v>
+      </c>
     </row>
     <row r="545" spans="1:15">
       <c r="A545" s="14" t="s">
-        <v>1237</v>
+        <v>1243</v>
       </c>
       <c r="B545" s="14" t="s">
-        <v>1238</v>
+        <v>1244</v>
       </c>
       <c r="O545" s="7" t="s">
-        <v>1239</v>
-      </c>
-    </row>
-    <row r="546" spans="1:15">
-      <c r="A546" s="14" t="s">
-        <v>1240</v>
-      </c>
-      <c r="B546" s="14" t="s">
-        <v>1241</v>
-      </c>
-      <c r="O546" s="7" t="s">
-        <v>1242</v>
-      </c>
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="A546" s="14"/>
+      <c r="B546" s="14"/>
     </row>
     <row r="547" spans="1:15">
       <c r="A547" s="14" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="B547" s="14" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="O547" s="7" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="548" spans="1:15">
       <c r="A548" s="14" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="B548" s="14" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="O548" s="7" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="549" spans="1:15">
       <c r="A549" s="14" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="B549" s="14" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="O549" s="7" t="s">
-        <v>1251</v>
-      </c>
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="A550" s="14"/>
+      <c r="B550" s="14"/>
     </row>
     <row r="551" spans="1:15">
       <c r="A551" s="14" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="B551" s="14" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="O551" s="7" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="552" spans="1:15">
       <c r="A552" s="14" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="B552" s="14" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="O552" s="7" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="553" spans="1:15">
       <c r="A553" s="14" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="B553" s="14" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
       <c r="O553" s="7" t="s">
-        <v>1259</v>
-      </c>
-    </row>
-    <row r="554" spans="1:2">
-      <c r="A554" s="14"/>
-      <c r="B554" s="14"/>
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="554" spans="1:15">
+      <c r="A554" s="14" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B554" s="14" t="s">
+        <v>1265</v>
+      </c>
+      <c r="O554" s="7" t="s">
+        <v>1266</v>
+      </c>
     </row>
     <row r="555" spans="1:15">
       <c r="A555" s="14" t="s">
-        <v>1260</v>
+        <v>1267</v>
       </c>
       <c r="B555" s="14" t="s">
-        <v>1261</v>
+        <v>1268</v>
       </c>
       <c r="O555" s="7" t="s">
-        <v>1262</v>
-      </c>
-    </row>
-    <row r="556" spans="1:15">
-      <c r="A556" s="14" t="s">
-        <v>1263</v>
-      </c>
-      <c r="B556" s="14" t="s">
-        <v>1264</v>
-      </c>
-      <c r="O556" s="7" t="s">
-        <v>1265</v>
-      </c>
-    </row>
-    <row r="557" spans="1:2">
-      <c r="A557" s="14"/>
-      <c r="B557" s="14"/>
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="557" spans="1:15">
+      <c r="A557" s="14" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B557" s="14" t="s">
+        <v>1271</v>
+      </c>
+      <c r="O557" s="7" t="s">
+        <v>1271</v>
+      </c>
     </row>
     <row r="558" spans="1:15">
       <c r="A558" s="14" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="B558" s="14" t="s">
-        <v>1267</v>
+        <v>1273</v>
       </c>
       <c r="O558" s="7" t="s">
-        <v>1268</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="559" spans="1:15">
       <c r="A559" s="14" t="s">
-        <v>1269</v>
+        <v>1275</v>
       </c>
       <c r="B559" s="14" t="s">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="O559" s="7" t="s">
-        <v>1271</v>
-      </c>
-    </row>
-    <row r="560" spans="1:15">
-      <c r="A560" s="14" t="s">
-        <v>1272</v>
-      </c>
-      <c r="B560" s="14" t="s">
-        <v>1270</v>
-      </c>
-      <c r="O560" s="7" t="s">
-        <v>1271</v>
-      </c>
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560" s="14"/>
+      <c r="B560" s="14"/>
     </row>
     <row r="561" spans="1:15">
-      <c r="A561" s="14"/>
-      <c r="B561" s="14"/>
-      <c r="O561" s="7"/>
+      <c r="A561" s="14" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B561" s="14" t="s">
+        <v>1279</v>
+      </c>
+      <c r="O561" s="7" t="s">
+        <v>1280</v>
+      </c>
     </row>
     <row r="562" spans="1:15">
       <c r="A562" s="14" t="s">
-        <v>1273</v>
+        <v>1281</v>
       </c>
       <c r="B562" s="14" t="s">
-        <v>1274</v>
+        <v>1282</v>
       </c>
       <c r="O562" s="7" t="s">
-        <v>1275</v>
-      </c>
-    </row>
-    <row r="563" spans="1:15">
-      <c r="A563" s="14" t="s">
-        <v>1276</v>
-      </c>
-      <c r="B563" s="14" t="s">
-        <v>1277</v>
-      </c>
-      <c r="O563" s="7" t="s">
-        <v>1278</v>
-      </c>
-    </row>
-    <row r="564" spans="1:2">
-      <c r="A564" s="14"/>
-      <c r="B564" s="14"/>
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563" s="14"/>
+      <c r="B563" s="14"/>
+    </row>
+    <row r="564" spans="1:15">
+      <c r="A564" s="14" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B564" s="14" t="s">
+        <v>1285</v>
+      </c>
+      <c r="O564" s="7" t="s">
+        <v>1286</v>
+      </c>
     </row>
     <row r="565" spans="1:15">
       <c r="A565" s="14" t="s">
-        <v>1279</v>
+        <v>1287</v>
       </c>
       <c r="B565" s="14" t="s">
-        <v>1280</v>
+        <v>1288</v>
       </c>
       <c r="O565" s="7" t="s">
-        <v>1281</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="566" spans="1:15">
       <c r="A566" s="14" t="s">
-        <v>1282</v>
+        <v>1290</v>
       </c>
       <c r="B566" s="14" t="s">
-        <v>1283</v>
+        <v>1288</v>
       </c>
       <c r="O566" s="7" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="567" spans="1:15">
-      <c r="A567" s="14" t="s">
-        <v>1285</v>
-      </c>
-      <c r="B567" s="14" t="s">
-        <v>1283</v>
-      </c>
-      <c r="O567" s="7" t="s">
-        <v>1284</v>
-      </c>
+      <c r="A567" s="14"/>
+      <c r="B567" s="14"/>
+      <c r="O567" s="7"/>
     </row>
     <row r="568" spans="1:15">
-      <c r="A568" s="14"/>
-      <c r="B568" s="14"/>
-      <c r="O568" s="7"/>
+      <c r="A568" s="14" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B568" s="14" t="s">
+        <v>1292</v>
+      </c>
+      <c r="O568" s="7" t="s">
+        <v>1293</v>
+      </c>
     </row>
     <row r="569" spans="1:15">
       <c r="A569" s="14" t="s">
-        <v>1286</v>
+        <v>1294</v>
       </c>
       <c r="B569" s="14" t="s">
-        <v>1287</v>
+        <v>1295</v>
       </c>
       <c r="O569" s="7" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="570" spans="1:15">
-      <c r="A570" s="14" t="s">
-        <v>1289</v>
-      </c>
-      <c r="B570" s="14" t="s">
-        <v>1290</v>
-      </c>
-      <c r="O570" s="7" t="s">
-        <v>1291</v>
-      </c>
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570" s="14"/>
+      <c r="B570" s="14"/>
     </row>
     <row r="571" spans="1:15">
       <c r="A571" s="14" t="s">
-        <v>1292</v>
+        <v>1297</v>
       </c>
       <c r="B571" s="14" t="s">
-        <v>1293</v>
+        <v>1298</v>
       </c>
       <c r="O571" s="7" t="s">
-        <v>1294</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="572" spans="1:15">
       <c r="A572" s="14" t="s">
-        <v>1295</v>
+        <v>1300</v>
       </c>
       <c r="B572" s="14" t="s">
-        <v>1296</v>
+        <v>1301</v>
       </c>
       <c r="O572" s="7" t="s">
-        <v>1297</v>
-      </c>
-    </row>
-    <row r="573" spans="1:2">
-      <c r="A573" s="14"/>
-      <c r="B573" s="14"/>
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="573" spans="1:15">
+      <c r="A573" s="14" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B573" s="14" t="s">
+        <v>1301</v>
+      </c>
+      <c r="O573" s="7" t="s">
+        <v>1302</v>
+      </c>
     </row>
     <row r="574" spans="1:15">
-      <c r="A574" s="14" t="s">
-        <v>1298</v>
-      </c>
-      <c r="B574" s="14" t="s">
-        <v>1299</v>
-      </c>
-      <c r="O574" s="2" t="s">
-        <v>1300</v>
-      </c>
+      <c r="A574" s="14"/>
+      <c r="B574" s="14"/>
+      <c r="O574" s="7"/>
     </row>
     <row r="575" spans="1:15">
       <c r="A575" s="14" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="B575" s="14" t="s">
-        <v>1302</v>
-      </c>
-      <c r="O575" s="2" t="s">
-        <v>1303</v>
+        <v>1305</v>
+      </c>
+      <c r="O575" s="7" t="s">
+        <v>1306</v>
       </c>
     </row>
     <row r="576" spans="1:15">
       <c r="A576" s="14" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="B576" s="14" t="s">
-        <v>1302</v>
-      </c>
-      <c r="O576" s="2" t="s">
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="577" spans="1:2">
-      <c r="A577" s="14"/>
-      <c r="B577" s="14"/>
+        <v>1308</v>
+      </c>
+      <c r="O576" s="7" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="577" spans="1:15">
+      <c r="A577" s="14" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B577" s="14" t="s">
+        <v>1311</v>
+      </c>
+      <c r="O577" s="7" t="s">
+        <v>1312</v>
+      </c>
     </row>
     <row r="578" spans="1:15">
       <c r="A578" s="14" t="s">
-        <v>1306</v>
+        <v>1313</v>
       </c>
       <c r="B578" s="14" t="s">
-        <v>1307</v>
-      </c>
-      <c r="O578" s="2" t="s">
-        <v>1308</v>
-      </c>
-    </row>
-    <row r="579" spans="1:15">
-      <c r="A579" s="14" t="s">
-        <v>1309</v>
-      </c>
-      <c r="B579" s="14" t="s">
-        <v>1310</v>
-      </c>
-      <c r="O579" s="2" t="s">
-        <v>1311</v>
-      </c>
+        <v>1314</v>
+      </c>
+      <c r="O578" s="7" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2">
+      <c r="A579" s="14"/>
+      <c r="B579" s="14"/>
     </row>
     <row r="580" spans="1:15">
       <c r="A580" s="14" t="s">
-        <v>1312</v>
+        <v>1316</v>
       </c>
       <c r="B580" s="14" t="s">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="O580" s="2" t="s">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="581" spans="1:2">
-      <c r="A581" s="14"/>
-      <c r="B581" s="14"/>
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="581" spans="1:15">
+      <c r="A581" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B581" s="14" t="s">
+        <v>1320</v>
+      </c>
+      <c r="O581" s="2" t="s">
+        <v>1321</v>
+      </c>
     </row>
     <row r="582" spans="1:15">
       <c r="A582" s="14" t="s">
-        <v>1313</v>
+        <v>1322</v>
       </c>
       <c r="B582" s="14" t="s">
-        <v>1314</v>
+        <v>1320</v>
       </c>
       <c r="O582" s="2" t="s">
-        <v>1315</v>
-      </c>
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2">
+      <c r="A583" s="14"/>
+      <c r="B583" s="14"/>
     </row>
     <row r="584" spans="1:15">
       <c r="A584" s="14" t="s">
-        <v>1316</v>
+        <v>1324</v>
       </c>
       <c r="B584" s="14" t="s">
-        <v>1317</v>
-      </c>
-      <c r="O584" s="7" t="s">
-        <v>1318</v>
+        <v>1325</v>
+      </c>
+      <c r="O584" s="2" t="s">
+        <v>1326</v>
       </c>
     </row>
     <row r="585" spans="1:15">
       <c r="A585" s="14" t="s">
-        <v>1319</v>
+        <v>1327</v>
       </c>
       <c r="B585" s="14" t="s">
-        <v>1320</v>
-      </c>
-      <c r="O585" s="7" t="s">
-        <v>1321</v>
+        <v>1328</v>
+      </c>
+      <c r="O585" s="2" t="s">
+        <v>1329</v>
       </c>
     </row>
     <row r="586" spans="1:15">
       <c r="A586" s="14" t="s">
-        <v>1322</v>
+        <v>1330</v>
       </c>
       <c r="B586" s="14" t="s">
-        <v>1323</v>
-      </c>
-      <c r="O586" s="7" t="s">
-        <v>1324</v>
-      </c>
-    </row>
-    <row r="587" spans="1:15">
-      <c r="A587" s="14" t="s">
-        <v>1325</v>
-      </c>
-      <c r="B587" s="14" t="s">
-        <v>1326</v>
-      </c>
-      <c r="O587" s="7" t="s">
-        <v>1327</v>
-      </c>
-    </row>
-    <row r="589" spans="1:15">
-      <c r="A589" s="14" t="s">
         <v>1328</v>
       </c>
-      <c r="B589" s="14" t="s">
+      <c r="O586" s="2" t="s">
         <v>1329</v>
       </c>
-      <c r="O589" s="2" t="s">
-        <v>1330</v>
+    </row>
+    <row r="587" spans="1:2">
+      <c r="A587" s="14"/>
+      <c r="B587" s="14"/>
+    </row>
+    <row r="588" spans="1:15">
+      <c r="A588" s="14" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B588" s="14" t="s">
+        <v>1332</v>
+      </c>
+      <c r="O588" s="2" t="s">
+        <v>1333</v>
       </c>
     </row>
     <row r="590" spans="1:15">
       <c r="A590" s="14" t="s">
-        <v>1331</v>
+        <v>1334</v>
       </c>
       <c r="B590" s="14" t="s">
-        <v>1332</v>
+        <v>1335</v>
       </c>
       <c r="O590" s="7" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="591" spans="1:15">
       <c r="A591" s="14" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="B591" s="14" t="s">
-        <v>1335</v>
+        <v>1338</v>
       </c>
       <c r="O591" s="7" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="592" spans="1:15">
       <c r="A592" s="14" t="s">
-        <v>1337</v>
+        <v>1340</v>
       </c>
       <c r="B592" s="14" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
       <c r="O592" s="7" t="s">
-        <v>1339</v>
-      </c>
-    </row>
-    <row r="593" spans="15:15">
-      <c r="O593" s="7"/>
-    </row>
-    <row r="594" spans="1:15">
-      <c r="A594" s="14" t="s">
-        <v>1340</v>
-      </c>
-      <c r="B594" s="14" t="s">
-        <v>1341</v>
-      </c>
-      <c r="O594" s="7" t="s">
         <v>1342</v>
+      </c>
+    </row>
+    <row r="593" spans="1:15">
+      <c r="A593" s="14" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B593" s="14" t="s">
+        <v>1344</v>
+      </c>
+      <c r="O593" s="7" t="s">
+        <v>1345</v>
       </c>
     </row>
     <row r="595" spans="1:15">
       <c r="A595" s="14" t="s">
-        <v>1343</v>
+        <v>1346</v>
       </c>
       <c r="B595" s="14" t="s">
-        <v>1344</v>
+        <v>1347</v>
       </c>
       <c r="O595" s="2" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="596" spans="1:15">
       <c r="A596" s="14" t="s">
-        <v>1346</v>
+        <v>1349</v>
       </c>
       <c r="B596" s="14" t="s">
-        <v>492</v>
+        <v>1350</v>
       </c>
       <c r="O596" s="7" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="597" spans="1:15">
       <c r="A597" s="14" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="B597" s="14" t="s">
-        <v>495</v>
+        <v>1353</v>
       </c>
       <c r="O597" s="7" t="s">
-        <v>1349</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="598" spans="1:15">
       <c r="A598" s="14" t="s">
-        <v>1350</v>
+        <v>1355</v>
       </c>
       <c r="B598" s="14" t="s">
-        <v>1351</v>
+        <v>1356</v>
       </c>
       <c r="O598" s="7" t="s">
-        <v>1352</v>
-      </c>
-    </row>
-    <row r="599" spans="1:15">
-      <c r="A599" s="14" t="s">
-        <v>1353</v>
-      </c>
-      <c r="B599" s="14" t="s">
-        <v>498</v>
-      </c>
-      <c r="O599" s="2" t="s">
-        <v>1354</v>
-      </c>
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="599" spans="15:15">
+      <c r="O599" s="7"/>
     </row>
     <row r="600" spans="1:15">
       <c r="A600" s="14" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
       <c r="B600" s="14" t="s">
-        <v>501</v>
-      </c>
-      <c r="O600" s="2" t="s">
-        <v>502</v>
+        <v>1359</v>
+      </c>
+      <c r="O600" s="7" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="601" spans="1:15">
       <c r="A601" s="14" t="s">
-        <v>1356</v>
+        <v>1361</v>
       </c>
       <c r="B601" s="14" t="s">
-        <v>507</v>
+        <v>1362</v>
       </c>
       <c r="O601" s="2" t="s">
-        <v>1357</v>
-      </c>
-    </row>
-    <row r="602" spans="1:2">
-      <c r="A602" s="14"/>
-      <c r="B602" s="14"/>
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="602" spans="1:15">
+      <c r="A602" s="14" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B602" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="O602" s="7" t="s">
+        <v>1365</v>
+      </c>
     </row>
     <row r="603" spans="1:15">
       <c r="A603" s="14" t="s">
-        <v>1358</v>
+        <v>1366</v>
       </c>
       <c r="B603" s="14" t="s">
-        <v>1359</v>
-      </c>
-      <c r="O603" s="2" t="s">
-        <v>1360</v>
+        <v>495</v>
+      </c>
+      <c r="O603" s="7" t="s">
+        <v>1367</v>
       </c>
     </row>
     <row r="604" spans="1:15">
       <c r="A604" s="14" t="s">
-        <v>1361</v>
+        <v>1368</v>
       </c>
       <c r="B604" s="14" t="s">
-        <v>1362</v>
-      </c>
-      <c r="O604" s="14" t="s">
-        <v>1363</v>
+        <v>1369</v>
+      </c>
+      <c r="O604" s="7" t="s">
+        <v>1370</v>
       </c>
     </row>
     <row r="605" spans="1:15">
       <c r="A605" s="14" t="s">
-        <v>1364</v>
+        <v>1371</v>
       </c>
       <c r="B605" s="14" t="s">
-        <v>1365</v>
-      </c>
-      <c r="O605" s="14" t="s">
-        <v>1366</v>
-      </c>
-    </row>
-    <row r="606" spans="1:2">
-      <c r="A606" s="14"/>
-      <c r="B606" s="14"/>
+        <v>498</v>
+      </c>
+      <c r="O605" s="2" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="606" spans="1:15">
+      <c r="A606" s="14" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B606" s="14" t="s">
+        <v>501</v>
+      </c>
+      <c r="O606" s="2" t="s">
+        <v>502</v>
+      </c>
     </row>
     <row r="607" spans="1:15">
       <c r="A607" s="14" t="s">
-        <v>1367</v>
+        <v>1374</v>
       </c>
       <c r="B607" s="14" t="s">
-        <v>1368</v>
+        <v>507</v>
       </c>
       <c r="O607" s="2" t="s">
-        <v>1369</v>
-      </c>
-    </row>
-    <row r="608" spans="1:15">
-      <c r="A608" s="14" t="s">
-        <v>1370</v>
-      </c>
-      <c r="B608" s="14" t="s">
-        <v>1371</v>
-      </c>
-      <c r="O608" s="2" t="s">
-        <v>1372</v>
-      </c>
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2">
+      <c r="A608" s="14"/>
+      <c r="B608" s="14"/>
     </row>
     <row r="609" spans="1:15">
       <c r="A609" s="14" t="s">
-        <v>1373</v>
+        <v>1376</v>
       </c>
       <c r="B609" s="14" t="s">
-        <v>1371</v>
+        <v>1377</v>
       </c>
       <c r="O609" s="2" t="s">
-        <v>1372</v>
-      </c>
-    </row>
-    <row r="610" spans="1:2">
-      <c r="A610" s="14"/>
-      <c r="B610" s="14"/>
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="610" spans="1:15">
+      <c r="A610" s="14" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B610" s="14" t="s">
+        <v>1380</v>
+      </c>
+      <c r="O610" s="14" t="s">
+        <v>1381</v>
+      </c>
     </row>
     <row r="611" spans="1:15">
       <c r="A611" s="14" t="s">
-        <v>1374</v>
+        <v>1382</v>
       </c>
       <c r="B611" s="14" t="s">
-        <v>995</v>
-      </c>
-      <c r="O611" s="7" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="612" spans="1:15">
-      <c r="A612" s="14" t="s">
-        <v>1375</v>
-      </c>
-      <c r="B612" s="14" t="s">
-        <v>1376</v>
-      </c>
-      <c r="O612" s="7" t="s">
-        <v>1377</v>
-      </c>
+        <v>1383</v>
+      </c>
+      <c r="O611" s="14" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2">
+      <c r="A612" s="14"/>
+      <c r="B612" s="14"/>
     </row>
     <row r="613" spans="1:15">
       <c r="A613" s="14" t="s">
-        <v>1378</v>
+        <v>1385</v>
       </c>
       <c r="B613" s="14" t="s">
-        <v>1379</v>
-      </c>
-      <c r="O613" s="7" t="s">
-        <v>733</v>
+        <v>1386</v>
+      </c>
+      <c r="O613" s="2" t="s">
+        <v>1387</v>
       </c>
     </row>
     <row r="614" spans="1:15">
       <c r="A614" s="14" t="s">
-        <v>1380</v>
+        <v>1388</v>
       </c>
       <c r="B614" s="14" t="s">
-        <v>1381</v>
-      </c>
-      <c r="O614" s="7" t="s">
-        <v>1382</v>
+        <v>1389</v>
+      </c>
+      <c r="O614" s="2" t="s">
+        <v>1390</v>
       </c>
     </row>
     <row r="615" spans="1:15">
       <c r="A615" s="14" t="s">
-        <v>1383</v>
+        <v>1391</v>
       </c>
       <c r="B615" s="14" t="s">
-        <v>1384</v>
-      </c>
-      <c r="O615" s="7" t="s">
-        <v>1385</v>
-      </c>
-    </row>
-    <row r="616" spans="1:15">
-      <c r="A616" s="14" t="s">
-        <v>1386</v>
-      </c>
-      <c r="B616" s="14" t="s">
-        <v>1387</v>
-      </c>
-      <c r="O616" s="7" t="s">
-        <v>1388</v>
-      </c>
+        <v>1389</v>
+      </c>
+      <c r="O615" s="2" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2">
+      <c r="A616" s="14"/>
+      <c r="B616" s="14"/>
     </row>
     <row r="617" spans="1:15">
       <c r="A617" s="14" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
       <c r="B617" s="14" t="s">
-        <v>1390</v>
+        <v>1013</v>
       </c>
       <c r="O617" s="7" t="s">
-        <v>1391</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="618" spans="1:15">
       <c r="A618" s="14" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="B618" s="14" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="O618" s="7" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="619" spans="1:15">
       <c r="A619" s="14" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="B619" s="14" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="O619" s="7" t="s">
-        <v>1397</v>
+        <v>742</v>
       </c>
     </row>
     <row r="620" spans="1:15">
@@ -14437,492 +14509,492 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="624" spans="15:15">
-      <c r="O624" s="13"/>
+    <row r="624" spans="1:15">
+      <c r="A624" s="14" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B624" s="14" t="s">
+        <v>1411</v>
+      </c>
+      <c r="O624" s="7" t="s">
+        <v>1412</v>
+      </c>
     </row>
     <row r="625" spans="1:15">
       <c r="A625" s="14" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="B625" s="14" t="s">
-        <v>1411</v>
-      </c>
-      <c r="O625" s="2" t="s">
-        <v>1412</v>
+        <v>1414</v>
+      </c>
+      <c r="O625" s="7" t="s">
+        <v>1415</v>
       </c>
     </row>
     <row r="626" spans="1:15">
       <c r="A626" s="14" t="s">
-        <v>1413</v>
+        <v>1416</v>
       </c>
       <c r="B626" s="14" t="s">
-        <v>1414</v>
+        <v>1417</v>
       </c>
       <c r="O626" s="7" t="s">
-        <v>1415</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="627" spans="1:15">
       <c r="A627" s="14" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
       <c r="B627" s="14" t="s">
-        <v>1417</v>
+        <v>1420</v>
       </c>
       <c r="O627" s="7" t="s">
-        <v>1418</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="628" spans="1:15">
       <c r="A628" s="14" t="s">
-        <v>1419</v>
+        <v>1422</v>
       </c>
       <c r="B628" s="14" t="s">
-        <v>1420</v>
+        <v>1423</v>
       </c>
       <c r="O628" s="7" t="s">
-        <v>1421</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="629" spans="1:15">
       <c r="A629" s="14" t="s">
-        <v>1422</v>
+        <v>1425</v>
       </c>
       <c r="B629" s="14" t="s">
-        <v>1423</v>
+        <v>1426</v>
       </c>
       <c r="O629" s="7" t="s">
-        <v>1424</v>
-      </c>
-    </row>
-    <row r="630" spans="1:2">
-      <c r="A630" s="14"/>
-      <c r="B630" s="14"/>
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="630" spans="15:15">
+      <c r="O630" s="13"/>
     </row>
     <row r="631" spans="1:15">
       <c r="A631" s="14" t="s">
-        <v>1425</v>
+        <v>1428</v>
       </c>
       <c r="B631" s="14" t="s">
-        <v>1426</v>
-      </c>
-      <c r="O631" s="7" t="s">
-        <v>1427</v>
+        <v>1429</v>
+      </c>
+      <c r="O631" s="2" t="s">
+        <v>1430</v>
       </c>
     </row>
     <row r="632" spans="1:15">
       <c r="A632" s="14" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
       <c r="B632" s="14" t="s">
-        <v>1429</v>
+        <v>1432</v>
       </c>
       <c r="O632" s="7" t="s">
-        <v>1430</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="633" spans="1:15">
       <c r="A633" s="14" t="s">
-        <v>1431</v>
+        <v>1434</v>
       </c>
       <c r="B633" s="14" t="s">
-        <v>1432</v>
+        <v>1435</v>
       </c>
       <c r="O633" s="7" t="s">
-        <v>1433</v>
-      </c>
-    </row>
-    <row r="634" spans="1:2">
-      <c r="A634" s="14"/>
-      <c r="B634" s="14"/>
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="634" spans="1:15">
+      <c r="A634" s="14" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B634" s="14" t="s">
+        <v>1438</v>
+      </c>
+      <c r="O634" s="7" t="s">
+        <v>1439</v>
+      </c>
     </row>
     <row r="635" spans="1:15">
       <c r="A635" s="14" t="s">
-        <v>1434</v>
+        <v>1440</v>
       </c>
       <c r="B635" s="14" t="s">
-        <v>1435</v>
+        <v>1441</v>
       </c>
       <c r="O635" s="7" t="s">
-        <v>1436</v>
-      </c>
-    </row>
-    <row r="636" spans="1:15">
-      <c r="A636" s="14" t="s">
-        <v>1437</v>
-      </c>
-      <c r="B636" s="14" t="s">
-        <v>1438</v>
-      </c>
-      <c r="O636" s="7" t="s">
-        <v>1439</v>
-      </c>
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2">
+      <c r="A636" s="14"/>
+      <c r="B636" s="14"/>
     </row>
     <row r="637" spans="1:15">
       <c r="A637" s="14" t="s">
-        <v>1440</v>
+        <v>1443</v>
       </c>
       <c r="B637" s="14" t="s">
-        <v>1441</v>
+        <v>1444</v>
       </c>
       <c r="O637" s="7" t="s">
-        <v>1442</v>
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="638" spans="1:15">
+      <c r="A638" s="14" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B638" s="14" t="s">
+        <v>1447</v>
+      </c>
+      <c r="O638" s="7" t="s">
+        <v>1448</v>
       </c>
     </row>
     <row r="639" spans="1:15">
       <c r="A639" s="14" t="s">
-        <v>1443</v>
+        <v>1449</v>
       </c>
       <c r="B639" s="14" t="s">
-        <v>1444</v>
-      </c>
-      <c r="O639" s="2" t="s">
-        <v>1445</v>
-      </c>
-    </row>
-    <row r="640" spans="1:15">
-      <c r="A640" s="14" t="s">
-        <v>1446</v>
-      </c>
-      <c r="B640" s="14" t="s">
-        <v>1447</v>
-      </c>
-      <c r="O640" s="7" t="s">
-        <v>1448</v>
-      </c>
+        <v>1450</v>
+      </c>
+      <c r="O639" s="7" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2">
+      <c r="A640" s="14"/>
+      <c r="B640" s="14"/>
     </row>
     <row r="641" spans="1:15">
       <c r="A641" s="14" t="s">
-        <v>1449</v>
+        <v>1452</v>
       </c>
       <c r="B641" s="14" t="s">
-        <v>1450</v>
+        <v>1453</v>
       </c>
       <c r="O641" s="7" t="s">
-        <v>1451</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="642" spans="1:15">
       <c r="A642" s="14" t="s">
-        <v>1452</v>
+        <v>1455</v>
       </c>
       <c r="B642" s="14" t="s">
-        <v>1453</v>
+        <v>1456</v>
       </c>
       <c r="O642" s="7" t="s">
-        <v>1454</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="643" spans="1:15">
       <c r="A643" s="14" t="s">
-        <v>1455</v>
+        <v>1458</v>
       </c>
       <c r="B643" s="14" t="s">
-        <v>1456</v>
+        <v>1459</v>
       </c>
       <c r="O643" s="7" t="s">
-        <v>1457</v>
-      </c>
-    </row>
-    <row r="644" spans="1:2">
-      <c r="A644" s="14"/>
-      <c r="B644" s="14"/>
-    </row>
-    <row r="645" spans="1:2">
-      <c r="A645" s="14"/>
-      <c r="B645" s="14"/>
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="645" spans="1:15">
+      <c r="A645" s="14" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B645" s="14" t="s">
+        <v>1462</v>
+      </c>
+      <c r="O645" s="2" t="s">
+        <v>1463</v>
+      </c>
     </row>
     <row r="646" spans="1:15">
       <c r="A646" s="14" t="s">
-        <v>1458</v>
+        <v>1464</v>
       </c>
       <c r="B646" s="14" t="s">
-        <v>1459</v>
-      </c>
-      <c r="O646" s="2" t="s">
-        <v>1460</v>
+        <v>1465</v>
+      </c>
+      <c r="O646" s="7" t="s">
+        <v>1466</v>
       </c>
     </row>
     <row r="647" spans="1:15">
       <c r="A647" s="14" t="s">
-        <v>1461</v>
+        <v>1467</v>
       </c>
       <c r="B647" s="14" t="s">
-        <v>1462</v>
-      </c>
-      <c r="O647" s="2" t="s">
-        <v>1463</v>
+        <v>1468</v>
+      </c>
+      <c r="O647" s="7" t="s">
+        <v>1469</v>
       </c>
     </row>
     <row r="648" spans="1:15">
       <c r="A648" s="14" t="s">
-        <v>1464</v>
+        <v>1470</v>
       </c>
       <c r="B648" s="14" t="s">
-        <v>1465</v>
-      </c>
-      <c r="O648" s="2" t="s">
-        <v>1463</v>
-      </c>
-    </row>
-    <row r="650" spans="1:15">
-      <c r="A650" s="14" t="s">
-        <v>1466</v>
-      </c>
-      <c r="B650" s="14" t="s">
-        <v>1467</v>
-      </c>
-      <c r="O650" s="2" t="s">
-        <v>1468</v>
-      </c>
-    </row>
-    <row r="651" spans="1:15">
-      <c r="A651" s="14" t="s">
-        <v>1469</v>
-      </c>
-      <c r="B651" s="14" t="s">
-        <v>1470</v>
-      </c>
-      <c r="O651" s="16" t="s">
-        <v>1397</v>
-      </c>
+        <v>1471</v>
+      </c>
+      <c r="O648" s="7" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="649" spans="1:15">
+      <c r="A649" s="14" t="s">
+        <v>1473</v>
+      </c>
+      <c r="B649" s="14" t="s">
+        <v>1474</v>
+      </c>
+      <c r="O649" s="7" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2">
+      <c r="A650" s="14"/>
+      <c r="B650" s="14"/>
+    </row>
+    <row r="651" spans="1:2">
+      <c r="A651" s="14"/>
+      <c r="B651" s="14"/>
     </row>
     <row r="652" spans="1:15">
       <c r="A652" s="14" t="s">
-        <v>1471</v>
+        <v>1476</v>
       </c>
       <c r="B652" s="14" t="s">
-        <v>1472</v>
-      </c>
-      <c r="O652" s="16" t="s">
-        <v>1473</v>
+        <v>1477</v>
+      </c>
+      <c r="O652" s="2" t="s">
+        <v>1478</v>
       </c>
     </row>
     <row r="653" spans="1:15">
       <c r="A653" s="14" t="s">
-        <v>1474</v>
+        <v>1479</v>
       </c>
       <c r="B653" s="14" t="s">
-        <v>1475</v>
-      </c>
-      <c r="O653" s="16" t="s">
-        <v>1476</v>
+        <v>1480</v>
+      </c>
+      <c r="O653" s="2" t="s">
+        <v>1481</v>
       </c>
     </row>
     <row r="654" spans="1:15">
       <c r="A654" s="14" t="s">
-        <v>1477</v>
+        <v>1482</v>
       </c>
       <c r="B654" s="14" t="s">
-        <v>1478</v>
-      </c>
-      <c r="O654" s="16" t="s">
-        <v>1382</v>
-      </c>
-    </row>
-    <row r="655" spans="1:15">
-      <c r="A655" s="14" t="s">
-        <v>1479</v>
-      </c>
-      <c r="B655" s="14" t="s">
-        <v>1480</v>
-      </c>
-      <c r="O655" s="16" t="s">
+        <v>1483</v>
+      </c>
+      <c r="O654" s="2" t="s">
         <v>1481</v>
       </c>
     </row>
     <row r="656" spans="1:15">
       <c r="A656" s="14" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="B656" s="14" t="s">
-        <v>1483</v>
-      </c>
-      <c r="O656" s="16" t="s">
-        <v>1484</v>
+        <v>1485</v>
+      </c>
+      <c r="O656" s="2" t="s">
+        <v>1486</v>
       </c>
     </row>
     <row r="657" spans="1:15">
       <c r="A657" s="14" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="B657" s="14" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="O657" s="16" t="s">
-        <v>1377</v>
-      </c>
-    </row>
-    <row r="658" spans="1:2">
-      <c r="A658" s="14"/>
-      <c r="B658" s="14"/>
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="658" spans="1:15">
+      <c r="A658" s="14" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B658" s="14" t="s">
+        <v>1490</v>
+      </c>
+      <c r="O658" s="16" t="s">
+        <v>1491</v>
+      </c>
     </row>
     <row r="659" spans="1:15">
       <c r="A659" s="14" t="s">
-        <v>1487</v>
+        <v>1492</v>
       </c>
       <c r="B659" s="14" t="s">
-        <v>1488</v>
+        <v>1493</v>
       </c>
       <c r="O659" s="16" t="s">
-        <v>1489</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="660" spans="1:15">
       <c r="A660" s="14" t="s">
-        <v>1490</v>
+        <v>1495</v>
       </c>
       <c r="B660" s="14" t="s">
-        <v>1491</v>
+        <v>1496</v>
       </c>
       <c r="O660" s="16" t="s">
-        <v>1492</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="661" spans="1:15">
       <c r="A661" s="14" t="s">
-        <v>1493</v>
+        <v>1497</v>
       </c>
       <c r="B661" s="14" t="s">
-        <v>1494</v>
+        <v>1498</v>
       </c>
       <c r="O661" s="16" t="s">
-        <v>1495</v>
-      </c>
-    </row>
-    <row r="662" spans="1:2">
-      <c r="A662" s="14"/>
-      <c r="B662" s="14"/>
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="662" spans="1:15">
+      <c r="A662" s="14" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B662" s="14" t="s">
+        <v>1501</v>
+      </c>
+      <c r="O662" s="16" t="s">
+        <v>1502</v>
+      </c>
     </row>
     <row r="663" spans="1:15">
       <c r="A663" s="14" t="s">
-        <v>1496</v>
+        <v>1503</v>
       </c>
       <c r="B663" s="14" t="s">
-        <v>1497</v>
-      </c>
-      <c r="O663" s="2" t="s">
-        <v>1498</v>
-      </c>
-    </row>
-    <row r="664" spans="1:15">
-      <c r="A664" s="14" t="s">
-        <v>1499</v>
-      </c>
-      <c r="B664" s="14" t="s">
-        <v>1500</v>
-      </c>
-      <c r="O664" s="2" t="s">
-        <v>1501</v>
-      </c>
+        <v>1504</v>
+      </c>
+      <c r="O663" s="16" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2">
+      <c r="A664" s="14"/>
+      <c r="B664" s="14"/>
     </row>
     <row r="665" spans="1:15">
       <c r="A665" s="14" t="s">
-        <v>1502</v>
+        <v>1505</v>
       </c>
       <c r="B665" s="14" t="s">
-        <v>1503</v>
-      </c>
-      <c r="O665" s="2" t="s">
-        <v>1504</v>
+        <v>1506</v>
+      </c>
+      <c r="O665" s="16" t="s">
+        <v>1507</v>
       </c>
     </row>
     <row r="666" spans="1:15">
       <c r="A666" s="14" t="s">
-        <v>1505</v>
+        <v>1508</v>
       </c>
       <c r="B666" s="14" t="s">
-        <v>1506</v>
-      </c>
-      <c r="O666" s="2" t="s">
-        <v>1507</v>
+        <v>1509</v>
+      </c>
+      <c r="O666" s="16" t="s">
+        <v>1510</v>
       </c>
     </row>
     <row r="667" spans="1:15">
       <c r="A667" s="14" t="s">
-        <v>1508</v>
+        <v>1511</v>
       </c>
       <c r="B667" s="14" t="s">
-        <v>1509</v>
-      </c>
-      <c r="O667" s="2" t="s">
-        <v>1510</v>
-      </c>
-    </row>
-    <row r="668" spans="1:15">
-      <c r="A668" s="14" t="s">
-        <v>1511</v>
-      </c>
-      <c r="B668" s="14" t="s">
         <v>1512</v>
       </c>
-      <c r="O668" s="2" t="s">
+      <c r="O667" s="16" t="s">
         <v>1513</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2">
+      <c r="A668" s="14"/>
+      <c r="B668" s="14"/>
+    </row>
+    <row r="669" spans="1:15">
+      <c r="A669" s="14" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B669" s="14" t="s">
+        <v>1515</v>
+      </c>
+      <c r="O669" s="2" t="s">
+        <v>1516</v>
       </c>
     </row>
     <row r="670" spans="1:15">
       <c r="A670" s="14" t="s">
-        <v>1514</v>
+        <v>1517</v>
       </c>
       <c r="B670" s="14" t="s">
-        <v>1515</v>
-      </c>
-      <c r="O670" s="7" t="s">
-        <v>1516</v>
+        <v>1518</v>
+      </c>
+      <c r="O670" s="2" t="s">
+        <v>1519</v>
       </c>
     </row>
     <row r="671" spans="1:15">
       <c r="A671" s="14" t="s">
-        <v>1517</v>
+        <v>1520</v>
       </c>
       <c r="B671" s="14" t="s">
-        <v>1518</v>
-      </c>
-      <c r="O671" s="16" t="s">
-        <v>1519</v>
+        <v>1521</v>
+      </c>
+      <c r="O671" s="2" t="s">
+        <v>1522</v>
       </c>
     </row>
     <row r="672" spans="1:15">
       <c r="A672" s="14" t="s">
-        <v>1520</v>
+        <v>1523</v>
       </c>
       <c r="B672" s="14" t="s">
-        <v>1521</v>
-      </c>
-      <c r="O672" s="16" t="s">
-        <v>1522</v>
+        <v>1524</v>
+      </c>
+      <c r="O672" s="2" t="s">
+        <v>1525</v>
       </c>
     </row>
     <row r="673" spans="1:15">
       <c r="A673" s="14" t="s">
-        <v>1523</v>
+        <v>1526</v>
       </c>
       <c r="B673" s="14" t="s">
-        <v>1524</v>
-      </c>
-      <c r="O673" s="16" t="s">
-        <v>1525</v>
+        <v>1527</v>
+      </c>
+      <c r="O673" s="2" t="s">
+        <v>1528</v>
       </c>
     </row>
     <row r="674" spans="1:15">
       <c r="A674" s="14" t="s">
-        <v>1526</v>
+        <v>1529</v>
       </c>
       <c r="B674" s="14" t="s">
-        <v>1527</v>
-      </c>
-      <c r="O674" s="16" t="s">
-        <v>1528</v>
-      </c>
-    </row>
-    <row r="675" spans="1:15">
-      <c r="A675" s="14" t="s">
-        <v>1529</v>
-      </c>
-      <c r="B675" s="14" t="s">
         <v>1530</v>
       </c>
-      <c r="O675" s="16" t="s">
+      <c r="O674" s="2" t="s">
         <v>1531</v>
       </c>
     </row>
@@ -14933,7 +15005,7 @@
       <c r="B676" s="14" t="s">
         <v>1533</v>
       </c>
-      <c r="O676" s="16" t="s">
+      <c r="O676" s="7" t="s">
         <v>1534</v>
       </c>
     </row>
@@ -14959,75 +15031,75 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="679" spans="1:2">
-      <c r="A679" s="14"/>
-      <c r="B679" s="14"/>
+    <row r="679" spans="1:15">
+      <c r="A679" s="14" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B679" s="14" t="s">
+        <v>1542</v>
+      </c>
+      <c r="O679" s="16" t="s">
+        <v>1543</v>
+      </c>
     </row>
     <row r="680" spans="1:15">
       <c r="A680" s="14" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="B680" s="14" t="s">
-        <v>1542</v>
-      </c>
-      <c r="O680" s="2" t="s">
-        <v>1543</v>
+        <v>1545</v>
+      </c>
+      <c r="O680" s="16" t="s">
+        <v>1546</v>
       </c>
     </row>
     <row r="681" spans="1:15">
       <c r="A681" s="14" t="s">
-        <v>1544</v>
+        <v>1547</v>
       </c>
       <c r="B681" s="14" t="s">
-        <v>1545</v>
-      </c>
-      <c r="O681" s="2" t="s">
-        <v>1546</v>
+        <v>1548</v>
+      </c>
+      <c r="O681" s="16" t="s">
+        <v>1549</v>
       </c>
     </row>
     <row r="682" spans="1:15">
       <c r="A682" s="14" t="s">
-        <v>1547</v>
+        <v>1550</v>
       </c>
       <c r="B682" s="14" t="s">
-        <v>1548</v>
-      </c>
-      <c r="O682" s="2" t="s">
-        <v>1549</v>
+        <v>1551</v>
+      </c>
+      <c r="O682" s="16" t="s">
+        <v>1552</v>
       </c>
     </row>
     <row r="683" spans="1:15">
       <c r="A683" s="14" t="s">
-        <v>1550</v>
+        <v>1553</v>
       </c>
       <c r="B683" s="14" t="s">
-        <v>1551</v>
-      </c>
-      <c r="O683" s="2" t="s">
-        <v>1552</v>
+        <v>1554</v>
+      </c>
+      <c r="O683" s="16" t="s">
+        <v>1555</v>
       </c>
     </row>
     <row r="684" spans="1:15">
       <c r="A684" s="14" t="s">
-        <v>1553</v>
+        <v>1556</v>
       </c>
       <c r="B684" s="14" t="s">
-        <v>1554</v>
-      </c>
-      <c r="O684" s="2" t="s">
-        <v>1555</v>
-      </c>
-    </row>
-    <row r="685" spans="1:15">
-      <c r="A685" s="14" t="s">
-        <v>1556</v>
-      </c>
-      <c r="B685" s="14" t="s">
         <v>1557</v>
       </c>
-      <c r="O685" s="2" t="s">
+      <c r="O684" s="16" t="s">
         <v>1558</v>
       </c>
+    </row>
+    <row r="685" spans="1:2">
+      <c r="A685" s="14"/>
+      <c r="B685" s="14"/>
     </row>
     <row r="686" spans="1:15">
       <c r="A686" s="14" t="s">
@@ -15036,7 +15108,7 @@
       <c r="B686" s="14" t="s">
         <v>1560</v>
       </c>
-      <c r="O686" s="17" t="s">
+      <c r="O686" s="2" t="s">
         <v>1561</v>
       </c>
     </row>
@@ -15047,7 +15119,7 @@
       <c r="B687" s="14" t="s">
         <v>1563</v>
       </c>
-      <c r="O687" s="17" t="s">
+      <c r="O687" s="2" t="s">
         <v>1564</v>
       </c>
     </row>
@@ -15058,7 +15130,7 @@
       <c r="B688" s="14" t="s">
         <v>1566</v>
       </c>
-      <c r="O688" s="17" t="s">
+      <c r="O688" s="2" t="s">
         <v>1567</v>
       </c>
     </row>
@@ -15080,7 +15152,7 @@
       <c r="B690" s="14" t="s">
         <v>1572</v>
       </c>
-      <c r="O690" s="18" t="s">
+      <c r="O690" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -15106,245 +15178,245 @@
         <v>1579</v>
       </c>
     </row>
+    <row r="693" spans="1:15">
+      <c r="A693" s="14" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B693" s="14" t="s">
+        <v>1581</v>
+      </c>
+      <c r="O693" s="17" t="s">
+        <v>1582</v>
+      </c>
+    </row>
     <row r="694" spans="1:15">
       <c r="A694" s="14" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="B694" s="14" t="s">
-        <v>1581</v>
-      </c>
-      <c r="O694" s="2" t="s">
-        <v>1582</v>
+        <v>1584</v>
+      </c>
+      <c r="O694" s="17" t="s">
+        <v>1585</v>
       </c>
     </row>
     <row r="695" spans="1:15">
       <c r="A695" s="14" t="s">
-        <v>1583</v>
+        <v>1586</v>
       </c>
       <c r="B695" s="14" t="s">
-        <v>1584</v>
+        <v>1587</v>
       </c>
       <c r="O695" s="2" t="s">
-        <v>1585</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="696" spans="1:15">
       <c r="A696" s="14" t="s">
-        <v>1586</v>
+        <v>1589</v>
       </c>
       <c r="B696" s="14" t="s">
-        <v>1587</v>
-      </c>
-      <c r="O696" s="2" t="s">
-        <v>1588</v>
+        <v>1590</v>
+      </c>
+      <c r="O696" s="18" t="s">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="697" spans="1:15">
+      <c r="A697" s="14" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B697" s="14" t="s">
+        <v>1593</v>
+      </c>
+      <c r="O697" s="2" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="698" spans="1:15">
-      <c r="A698" s="2" t="s">
-        <v>1589</v>
-      </c>
-      <c r="B698" s="2" t="s">
-        <v>1590</v>
-      </c>
-      <c r="O698" s="2" t="s">
-        <v>1591</v>
-      </c>
-    </row>
-    <row r="699" spans="1:15">
-      <c r="A699" s="2" t="s">
-        <v>1592</v>
-      </c>
-      <c r="B699" s="2" t="s">
-        <v>1593</v>
-      </c>
-      <c r="O699" s="2" t="s">
-        <v>1594</v>
+      <c r="A698" s="14" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B698" s="14" t="s">
+        <v>1596</v>
+      </c>
+      <c r="O698" s="17" t="s">
+        <v>1597</v>
       </c>
     </row>
     <row r="700" spans="1:15">
-      <c r="A700" s="2" t="s">
-        <v>1595</v>
-      </c>
-      <c r="B700" s="2" t="s">
-        <v>1593</v>
+      <c r="A700" s="14" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B700" s="14" t="s">
+        <v>1599</v>
       </c>
       <c r="O700" s="2" t="s">
-        <v>1594</v>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="701" spans="1:15">
+      <c r="A701" s="14" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B701" s="14" t="s">
+        <v>1602</v>
+      </c>
+      <c r="O701" s="2" t="s">
+        <v>1603</v>
       </c>
     </row>
     <row r="702" spans="1:15">
-      <c r="A702" s="2" t="s">
-        <v>1596</v>
-      </c>
-      <c r="B702" s="2" t="s">
-        <v>1597</v>
+      <c r="A702" s="14" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B702" s="14" t="s">
+        <v>1605</v>
       </c>
       <c r="O702" s="2" t="s">
-        <v>1598</v>
-      </c>
-    </row>
-    <row r="703" spans="1:15">
-      <c r="A703" s="2" t="s">
-        <v>1599</v>
-      </c>
-      <c r="B703" s="2" t="s">
-        <v>1600</v>
-      </c>
-      <c r="O703" s="2" t="s">
-        <v>1601</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="704" spans="1:15">
       <c r="A704" s="2" t="s">
-        <v>1602</v>
+        <v>1607</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>1600</v>
+        <v>1608</v>
       </c>
       <c r="O704" s="2" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="709" s="1" customFormat="1" spans="1:15">
-      <c r="A709" s="1" t="s">
-        <v>1603</v>
-      </c>
-      <c r="B709" s="1" t="s">
-        <v>1604</v>
-      </c>
-      <c r="O709" s="1" t="s">
-        <v>1605</v>
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="705" spans="1:15">
+      <c r="A705" s="2" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B705" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="O705" s="2" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="706" spans="1:15">
+      <c r="A706" s="2" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B706" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="O706" s="2" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="708" spans="1:15">
+      <c r="A708" s="2" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B708" s="2" t="s">
+        <v>1615</v>
+      </c>
+      <c r="O708" s="2" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="709" spans="1:15">
+      <c r="A709" s="2" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B709" s="2" t="s">
+        <v>1618</v>
+      </c>
+      <c r="O709" s="2" t="s">
+        <v>1619</v>
       </c>
     </row>
     <row r="710" spans="1:15">
       <c r="A710" s="2" t="s">
-        <v>1606</v>
+        <v>1620</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>1607</v>
+        <v>1618</v>
       </c>
       <c r="O710" s="2" t="s">
-        <v>1608</v>
-      </c>
-    </row>
-    <row r="711" spans="1:15">
-      <c r="A711" s="2" t="s">
-        <v>1609</v>
-      </c>
-      <c r="B711" s="2" t="s">
-        <v>1610</v>
-      </c>
-      <c r="O711" s="2" t="s">
-        <v>1611</v>
-      </c>
-    </row>
-    <row r="712" spans="1:15">
-      <c r="A712" s="2" t="s">
-        <v>1612</v>
-      </c>
-      <c r="B712" s="2" t="s">
-        <v>1613</v>
-      </c>
-      <c r="O712" s="2" t="s">
-        <v>1614</v>
-      </c>
-    </row>
-    <row r="713" spans="1:15">
-      <c r="A713" s="2" t="s">
-        <v>1615</v>
-      </c>
-      <c r="B713" s="2" t="s">
-        <v>1616</v>
-      </c>
-      <c r="O713" s="2" t="s">
-        <v>1617</v>
-      </c>
-    </row>
-    <row r="714" spans="1:15">
-      <c r="A714" s="2" t="s">
-        <v>1618</v>
-      </c>
-      <c r="B714" s="2" t="s">
         <v>1619</v>
       </c>
-      <c r="O714" s="2" t="s">
-        <v>1620</v>
-      </c>
-    </row>
-    <row r="715" spans="1:15">
-      <c r="A715" s="2" t="s">
+    </row>
+    <row r="715" s="1" customFormat="1" spans="1:15">
+      <c r="A715" s="1" t="s">
         <v>1621</v>
       </c>
-      <c r="B715" s="2" t="s">
+      <c r="B715" s="1" t="s">
         <v>1622</v>
       </c>
-      <c r="O715" s="2" t="s">
+      <c r="O715" s="1" t="s">
         <v>1623</v>
       </c>
     </row>
+    <row r="716" spans="1:15">
+      <c r="A716" s="2" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B716" s="2" t="s">
+        <v>1625</v>
+      </c>
+      <c r="O716" s="2" t="s">
+        <v>1626</v>
+      </c>
+    </row>
     <row r="717" spans="1:15">
-      <c r="A717" s="19" t="s">
-        <v>1624</v>
+      <c r="A717" s="2" t="s">
+        <v>1627</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>1625</v>
+        <v>1628</v>
       </c>
       <c r="O717" s="2" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="718" spans="1:15">
-      <c r="A718" s="19" t="s">
-        <v>1627</v>
+      <c r="A718" s="2" t="s">
+        <v>1630</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="O718" s="2" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="719" spans="1:15">
-      <c r="A719" s="19" t="s">
-        <v>1630</v>
+      <c r="A719" s="2" t="s">
+        <v>1633</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="O719" s="2" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="720" spans="1:15">
-      <c r="A720" s="19" t="s">
-        <v>1633</v>
+      <c r="A720" s="2" t="s">
+        <v>1636</v>
       </c>
       <c r="B720" s="2" t="s">
-        <v>1634</v>
+        <v>1637</v>
       </c>
       <c r="O720" s="2" t="s">
-        <v>1635</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="721" spans="1:15">
-      <c r="A721" s="19" t="s">
-        <v>1636</v>
+      <c r="A721" s="2" t="s">
+        <v>1639</v>
       </c>
       <c r="B721" s="2" t="s">
-        <v>1637</v>
+        <v>1640</v>
       </c>
       <c r="O721" s="2" t="s">
-        <v>1638</v>
-      </c>
-    </row>
-    <row r="722" spans="1:15">
-      <c r="A722" s="19" t="s">
-        <v>1639</v>
-      </c>
-      <c r="B722" s="2" t="s">
-        <v>1640</v>
-      </c>
-      <c r="O722" s="2" t="s">
         <v>1641</v>
       </c>
     </row>
@@ -15370,69 +15442,69 @@
         <v>1647</v>
       </c>
     </row>
+    <row r="725" spans="1:15">
+      <c r="A725" s="19" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B725" s="2" t="s">
+        <v>1649</v>
+      </c>
+      <c r="O725" s="2" t="s">
+        <v>1650</v>
+      </c>
+    </row>
     <row r="726" spans="1:15">
       <c r="A726" s="19" t="s">
-        <v>1648</v>
-      </c>
-      <c r="B726" s="19" t="s">
-        <v>1649</v>
+        <v>1651</v>
+      </c>
+      <c r="B726" s="2" t="s">
+        <v>1652</v>
       </c>
       <c r="O726" s="2" t="s">
-        <v>1650</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="727" spans="1:15">
       <c r="A727" s="19" t="s">
-        <v>1651</v>
-      </c>
-      <c r="B727" s="19" t="s">
-        <v>1652</v>
+        <v>1654</v>
+      </c>
+      <c r="B727" s="2" t="s">
+        <v>1655</v>
       </c>
       <c r="O727" s="2" t="s">
-        <v>1653</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="728" spans="1:15">
       <c r="A728" s="19" t="s">
-        <v>1654</v>
-      </c>
-      <c r="B728" s="19" t="s">
-        <v>1655</v>
+        <v>1657</v>
+      </c>
+      <c r="B728" s="2" t="s">
+        <v>1658</v>
       </c>
       <c r="O728" s="2" t="s">
-        <v>1656</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="729" spans="1:15">
       <c r="A729" s="19" t="s">
-        <v>1657</v>
-      </c>
-      <c r="B729" s="19" t="s">
-        <v>1658</v>
+        <v>1660</v>
+      </c>
+      <c r="B729" s="2" t="s">
+        <v>1661</v>
       </c>
       <c r="O729" s="2" t="s">
-        <v>1659</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="730" spans="1:15">
       <c r="A730" s="19" t="s">
-        <v>1660</v>
-      </c>
-      <c r="B730" s="19" t="s">
-        <v>1661</v>
+        <v>1663</v>
+      </c>
+      <c r="B730" s="2" t="s">
+        <v>1664</v>
       </c>
       <c r="O730" s="2" t="s">
-        <v>1662</v>
-      </c>
-    </row>
-    <row r="731" spans="1:15">
-      <c r="A731" s="19" t="s">
-        <v>1663</v>
-      </c>
-      <c r="B731" s="19" t="s">
-        <v>1664</v>
-      </c>
-      <c r="O731" s="2" t="s">
         <v>1665</v>
       </c>
     </row>
@@ -15441,595 +15513,469 @@
         <v>1666</v>
       </c>
       <c r="B732" s="19" t="s">
-        <v>1664</v>
+        <v>1667</v>
       </c>
       <c r="O732" s="2" t="s">
-        <v>1667</v>
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="733" spans="1:15">
+      <c r="A733" s="19" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B733" s="19" t="s">
+        <v>1670</v>
+      </c>
+      <c r="O733" s="2" t="s">
+        <v>1671</v>
       </c>
     </row>
     <row r="734" spans="1:15">
-      <c r="A734" s="2" t="s">
-        <v>1668</v>
-      </c>
-      <c r="B734" s="2" t="s">
-        <v>1669</v>
+      <c r="A734" s="19" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B734" s="19" t="s">
+        <v>1673</v>
       </c>
       <c r="O734" s="2" t="s">
-        <v>1670</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="735" spans="1:15">
-      <c r="A735" s="2" t="s">
-        <v>1671</v>
-      </c>
-      <c r="B735" s="2" t="s">
-        <v>1672</v>
+      <c r="A735" s="19" t="s">
+        <v>1675</v>
+      </c>
+      <c r="B735" s="19" t="s">
+        <v>1676</v>
       </c>
       <c r="O735" s="2" t="s">
-        <v>1673</v>
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="736" spans="1:15">
+      <c r="A736" s="19" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B736" s="19" t="s">
+        <v>1679</v>
+      </c>
+      <c r="O736" s="2" t="s">
+        <v>1680</v>
       </c>
     </row>
     <row r="737" spans="1:15">
-      <c r="A737" s="2" t="s">
-        <v>1674</v>
-      </c>
-      <c r="B737" s="2" t="s">
-        <v>1675</v>
+      <c r="A737" s="19" t="s">
+        <v>1681</v>
+      </c>
+      <c r="B737" s="19" t="s">
+        <v>1682</v>
       </c>
       <c r="O737" s="2" t="s">
-        <v>1676</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="738" spans="1:15">
-      <c r="A738" s="2" t="s">
-        <v>1677</v>
-      </c>
-      <c r="B738" s="2" t="s">
-        <v>1678</v>
+      <c r="A738" s="19" t="s">
+        <v>1684</v>
+      </c>
+      <c r="B738" s="19" t="s">
+        <v>1682</v>
       </c>
       <c r="O738" s="2" t="s">
-        <v>1679</v>
-      </c>
-    </row>
-    <row r="739" spans="1:15">
-      <c r="A739" s="2" t="s">
-        <v>1680</v>
-      </c>
-      <c r="B739" s="2" t="s">
-        <v>1681</v>
-      </c>
-      <c r="O739" s="2" t="s">
-        <v>1682</v>
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="740" spans="1:15">
+      <c r="A740" s="2" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B740" s="2" t="s">
+        <v>1687</v>
+      </c>
+      <c r="O740" s="2" t="s">
+        <v>1688</v>
       </c>
     </row>
     <row r="741" spans="1:15">
       <c r="A741" s="2" t="s">
-        <v>1683</v>
+        <v>1689</v>
       </c>
       <c r="B741" s="2" t="s">
-        <v>1684</v>
+        <v>1690</v>
       </c>
       <c r="O741" s="2" t="s">
-        <v>1685</v>
-      </c>
-    </row>
-    <row r="742" spans="1:15">
-      <c r="A742" s="2" t="s">
-        <v>1686</v>
-      </c>
-      <c r="B742" s="2" t="s">
-        <v>1687</v>
-      </c>
-      <c r="O742" s="2" t="s">
-        <v>1688</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="743" spans="1:15">
       <c r="A743" s="2" t="s">
-        <v>1689</v>
+        <v>1692</v>
       </c>
       <c r="B743" s="2" t="s">
-        <v>1690</v>
+        <v>1693</v>
       </c>
       <c r="O743" s="2" t="s">
-        <v>1691</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="744" spans="1:15">
       <c r="A744" s="2" t="s">
-        <v>1692</v>
+        <v>1695</v>
       </c>
       <c r="B744" s="2" t="s">
-        <v>1693</v>
+        <v>1696</v>
       </c>
       <c r="O744" s="2" t="s">
-        <v>1694</v>
-      </c>
-    </row>
-    <row r="745" ht="28.5" spans="1:15">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="745" spans="1:15">
       <c r="A745" s="2" t="s">
-        <v>1695</v>
-      </c>
-      <c r="B745" s="13" t="s">
-        <v>1696</v>
-      </c>
-      <c r="O745" s="13" t="s">
-        <v>1697</v>
-      </c>
-    </row>
-    <row r="746" ht="28.5" spans="1:15">
-      <c r="A746" s="2" t="s">
         <v>1698</v>
       </c>
-      <c r="B746" s="13" t="s">
+      <c r="B745" s="2" t="s">
         <v>1699</v>
       </c>
-      <c r="O746" s="13" t="s">
-        <v>1699</v>
+      <c r="O745" s="2" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="747" spans="1:15">
+      <c r="A747" s="2" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B747" s="2" t="s">
+        <v>1702</v>
+      </c>
+      <c r="O747" s="2" t="s">
+        <v>1703</v>
       </c>
     </row>
     <row r="748" spans="1:15">
       <c r="A748" s="2" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="B748" s="2" t="s">
-        <v>1701</v>
+        <v>1705</v>
       </c>
       <c r="O748" s="2" t="s">
-        <v>1702</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="749" spans="1:15">
       <c r="A749" s="2" t="s">
-        <v>1703</v>
+        <v>1707</v>
       </c>
       <c r="B749" s="2" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="O749" s="2" t="s">
-        <v>1705</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="750" spans="1:15">
       <c r="A750" s="2" t="s">
-        <v>1706</v>
+        <v>1710</v>
       </c>
       <c r="B750" s="2" t="s">
-        <v>1707</v>
+        <v>1711</v>
       </c>
       <c r="O750" s="2" t="s">
-        <v>1708</v>
-      </c>
-    </row>
-    <row r="751" spans="1:15">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="751" ht="28.5" spans="1:15">
       <c r="A751" s="2" t="s">
-        <v>1709</v>
-      </c>
-      <c r="B751" s="2" t="s">
-        <v>1710</v>
-      </c>
-      <c r="O751" s="2" t="s">
-        <v>1711</v>
-      </c>
-    </row>
-    <row r="752" spans="1:15">
+        <v>1713</v>
+      </c>
+      <c r="B751" s="13" t="s">
+        <v>1714</v>
+      </c>
+      <c r="O751" s="13" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="752" ht="28.5" spans="1:15">
       <c r="A752" s="2" t="s">
-        <v>1712</v>
-      </c>
-      <c r="B752" s="2" t="s">
-        <v>1713</v>
-      </c>
-      <c r="O752" s="2" t="s">
-        <v>1714</v>
-      </c>
-    </row>
-    <row r="753" spans="1:15">
-      <c r="A753" s="2" t="s">
-        <v>1715</v>
-      </c>
-      <c r="B753" s="2" t="s">
         <v>1716</v>
       </c>
-      <c r="O753" s="2" t="s">
+      <c r="B752" s="13" t="s">
         <v>1717</v>
+      </c>
+      <c r="O752" s="13" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="754" spans="1:15">
+      <c r="A754" s="2" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B754" s="2" t="s">
+        <v>1719</v>
+      </c>
+      <c r="O754" s="2" t="s">
+        <v>1720</v>
       </c>
     </row>
     <row r="755" spans="1:15">
       <c r="A755" s="2" t="s">
-        <v>1718</v>
+        <v>1721</v>
       </c>
       <c r="B755" s="2" t="s">
-        <v>1719</v>
-      </c>
-      <c r="O755" s="7" t="s">
-        <v>1720</v>
+        <v>1722</v>
+      </c>
+      <c r="O755" s="2" t="s">
+        <v>1723</v>
       </c>
     </row>
     <row r="756" spans="1:15">
       <c r="A756" s="2" t="s">
-        <v>1721</v>
+        <v>1724</v>
       </c>
       <c r="B756" s="2" t="s">
-        <v>1722</v>
-      </c>
-      <c r="O756" s="7" t="s">
-        <v>1723</v>
+        <v>1725</v>
+      </c>
+      <c r="O756" s="2" t="s">
+        <v>1726</v>
       </c>
     </row>
     <row r="757" spans="1:15">
       <c r="A757" s="2" t="s">
-        <v>1724</v>
+        <v>1727</v>
       </c>
       <c r="B757" s="2" t="s">
-        <v>1725</v>
-      </c>
-      <c r="O757" s="7" t="s">
-        <v>1726</v>
+        <v>1728</v>
+      </c>
+      <c r="O757" s="2" t="s">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="758" spans="1:15">
+      <c r="A758" s="2" t="s">
+        <v>1730</v>
+      </c>
+      <c r="B758" s="2" t="s">
+        <v>1731</v>
+      </c>
+      <c r="O758" s="2" t="s">
+        <v>1732</v>
       </c>
     </row>
     <row r="759" spans="1:15">
       <c r="A759" s="2" t="s">
-        <v>1727</v>
+        <v>1733</v>
       </c>
       <c r="B759" s="2" t="s">
-        <v>1728</v>
+        <v>1734</v>
       </c>
       <c r="O759" s="2" t="s">
-        <v>1729</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="761" spans="1:15">
       <c r="A761" s="2" t="s">
-        <v>1730</v>
+        <v>1736</v>
       </c>
       <c r="B761" s="2" t="s">
-        <v>1731</v>
+        <v>1737</v>
       </c>
       <c r="O761" s="7" t="s">
-        <v>1732</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="762" spans="1:15">
       <c r="A762" s="2" t="s">
-        <v>1733</v>
+        <v>1739</v>
       </c>
       <c r="B762" s="2" t="s">
-        <v>1734</v>
+        <v>1740</v>
       </c>
       <c r="O762" s="7" t="s">
-        <v>1735</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="763" spans="1:15">
       <c r="A763" s="2" t="s">
-        <v>1736</v>
+        <v>1742</v>
       </c>
       <c r="B763" s="2" t="s">
-        <v>1737</v>
+        <v>1743</v>
       </c>
       <c r="O763" s="7" t="s">
-        <v>1738</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="765" spans="1:15">
       <c r="A765" s="2" t="s">
-        <v>1739</v>
+        <v>1745</v>
       </c>
       <c r="B765" s="2" t="s">
-        <v>1740</v>
+        <v>1746</v>
       </c>
       <c r="O765" s="2" t="s">
-        <v>1741</v>
-      </c>
-    </row>
-    <row r="766" spans="1:15">
-      <c r="A766" s="2" t="s">
-        <v>1742</v>
-      </c>
-      <c r="B766" s="2" t="s">
-        <v>1743</v>
-      </c>
-      <c r="O766" s="2" t="s">
-        <v>1744</v>
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="767" spans="1:15">
+      <c r="A767" s="2" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B767" s="2" t="s">
+        <v>1749</v>
+      </c>
+      <c r="O767" s="7" t="s">
+        <v>1750</v>
       </c>
     </row>
     <row r="768" spans="1:15">
       <c r="A768" s="2" t="s">
-        <v>1745</v>
+        <v>1751</v>
       </c>
       <c r="B768" s="2" t="s">
-        <v>1746</v>
-      </c>
-      <c r="O768" s="2" t="s">
-        <v>1747</v>
+        <v>1752</v>
+      </c>
+      <c r="O768" s="7" t="s">
+        <v>1753</v>
       </c>
     </row>
     <row r="769" spans="1:15">
       <c r="A769" s="2" t="s">
-        <v>1748</v>
+        <v>1754</v>
       </c>
       <c r="B769" s="2" t="s">
-        <v>1749</v>
-      </c>
-      <c r="O769" s="2" t="s">
-        <v>1750</v>
+        <v>1755</v>
+      </c>
+      <c r="O769" s="7" t="s">
+        <v>1756</v>
       </c>
     </row>
     <row r="771" spans="1:15">
       <c r="A771" s="2" t="s">
-        <v>1751</v>
+        <v>1757</v>
       </c>
       <c r="B771" s="2" t="s">
-        <v>1752</v>
+        <v>1758</v>
       </c>
       <c r="O771" s="2" t="s">
-        <v>1753</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="772" spans="1:15">
       <c r="A772" s="2" t="s">
-        <v>1754</v>
+        <v>1760</v>
       </c>
       <c r="B772" s="2" t="s">
-        <v>1755</v>
+        <v>1761</v>
       </c>
       <c r="O772" s="2" t="s">
-        <v>1756</v>
-      </c>
-    </row>
-    <row r="773" spans="1:15">
-      <c r="A773" s="2" t="s">
-        <v>1757</v>
-      </c>
-      <c r="B773" s="2" t="s">
-        <v>1758</v>
-      </c>
-      <c r="O773" s="20" t="s">
-        <v>1759</v>
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="774" spans="1:15">
+      <c r="A774" s="2" t="s">
+        <v>1763</v>
+      </c>
+      <c r="B774" s="2" t="s">
+        <v>1764</v>
+      </c>
+      <c r="O774" s="2" t="s">
+        <v>1765</v>
       </c>
     </row>
     <row r="775" spans="1:15">
       <c r="A775" s="2" t="s">
-        <v>1760</v>
+        <v>1766</v>
       </c>
       <c r="B775" s="2" t="s">
-        <v>1761</v>
+        <v>1767</v>
       </c>
       <c r="O775" s="2" t="s">
-        <v>1762</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="777" spans="1:15">
       <c r="A777" s="2" t="s">
-        <v>1763</v>
+        <v>1769</v>
       </c>
       <c r="B777" s="2" t="s">
-        <v>1764</v>
+        <v>1770</v>
       </c>
       <c r="O777" s="2" t="s">
-        <v>1765</v>
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="778" spans="1:15">
+      <c r="A778" s="2" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B778" s="2" t="s">
+        <v>1773</v>
+      </c>
+      <c r="O778" s="2" t="s">
+        <v>1774</v>
       </c>
     </row>
     <row r="779" spans="1:15">
       <c r="A779" s="2" t="s">
-        <v>1766</v>
+        <v>1775</v>
       </c>
       <c r="B779" s="2" t="s">
-        <v>1767</v>
-      </c>
-      <c r="O779" s="2" t="s">
-        <v>1768</v>
-      </c>
-    </row>
-    <row r="780" spans="1:15">
-      <c r="A780" s="2" t="s">
-        <v>1769</v>
-      </c>
-      <c r="B780" s="2" t="s">
-        <v>1770</v>
-      </c>
-      <c r="O780" s="2" t="s">
-        <v>1771</v>
-      </c>
-    </row>
-    <row r="782" spans="1:25">
-      <c r="A782" s="7" t="s">
-        <v>1772</v>
-      </c>
-      <c r="B782" s="7" t="s">
-        <v>1773</v>
-      </c>
-      <c r="D782" s="7"/>
-      <c r="E782" s="7"/>
-      <c r="F782" s="7"/>
-      <c r="G782" s="7"/>
-      <c r="H782" s="7"/>
-      <c r="I782" s="7"/>
-      <c r="J782" s="7"/>
-      <c r="K782" s="7"/>
-      <c r="L782" s="7"/>
-      <c r="M782" s="7"/>
-      <c r="N782" s="7"/>
-      <c r="O782" s="7" t="s">
-        <v>1774</v>
-      </c>
-      <c r="P782" s="7"/>
-      <c r="Q782" s="7"/>
-      <c r="R782" s="7"/>
-      <c r="S782" s="7"/>
-      <c r="T782" s="7"/>
-      <c r="U782" s="7"/>
-      <c r="V782" s="7"/>
-      <c r="W782" s="7"/>
-      <c r="X782" s="7"/>
-      <c r="Y782" s="7"/>
-    </row>
-    <row r="783" spans="1:25">
-      <c r="A783" s="7" t="s">
-        <v>1775</v>
-      </c>
-      <c r="B783" s="7" t="s">
         <v>1776</v>
       </c>
-      <c r="D783" s="7"/>
-      <c r="E783" s="7"/>
-      <c r="F783" s="7"/>
-      <c r="G783" s="7"/>
-      <c r="H783" s="7"/>
-      <c r="I783" s="7"/>
-      <c r="J783" s="7"/>
-      <c r="K783" s="7"/>
-      <c r="L783" s="7"/>
-      <c r="M783" s="7"/>
-      <c r="N783" s="7"/>
-      <c r="O783" s="7" t="s">
+      <c r="O779" s="20" t="s">
         <v>1777</v>
       </c>
-      <c r="P783" s="7"/>
-      <c r="Q783" s="7"/>
-      <c r="R783" s="7"/>
-      <c r="S783" s="7"/>
-      <c r="T783" s="7"/>
-      <c r="U783" s="7"/>
-      <c r="V783" s="7"/>
-      <c r="W783" s="7"/>
-      <c r="X783" s="7"/>
-      <c r="Y783" s="7"/>
-    </row>
-    <row r="784" spans="1:25">
-      <c r="A784" s="7" t="s">
+    </row>
+    <row r="781" spans="1:15">
+      <c r="A781" s="2" t="s">
         <v>1778</v>
       </c>
-      <c r="B784" s="7" t="s">
+      <c r="B781" s="2" t="s">
         <v>1779</v>
       </c>
-      <c r="D784" s="7"/>
-      <c r="E784" s="7"/>
-      <c r="F784" s="7"/>
-      <c r="G784" s="7"/>
-      <c r="H784" s="7"/>
-      <c r="I784" s="7"/>
-      <c r="J784" s="7"/>
-      <c r="K784" s="7"/>
-      <c r="L784" s="7"/>
-      <c r="M784" s="7"/>
-      <c r="N784" s="7"/>
-      <c r="O784" s="7" t="s">
+      <c r="O781" s="2" t="s">
         <v>1780</v>
       </c>
-      <c r="P784" s="7"/>
-      <c r="Q784" s="7"/>
-      <c r="R784" s="7"/>
-      <c r="S784" s="7"/>
-      <c r="T784" s="7"/>
-      <c r="U784" s="7"/>
-      <c r="V784" s="7"/>
-      <c r="W784" s="7"/>
-      <c r="X784" s="7"/>
-      <c r="Y784" s="7"/>
-    </row>
-    <row r="785" spans="1:25">
-      <c r="A785" s="7" t="s">
+    </row>
+    <row r="783" spans="1:15">
+      <c r="A783" s="2" t="s">
         <v>1781</v>
       </c>
-      <c r="B785" s="7" t="s">
+      <c r="B783" s="2" t="s">
         <v>1782</v>
       </c>
-      <c r="D785" s="7"/>
-      <c r="E785" s="7"/>
-      <c r="F785" s="7"/>
-      <c r="G785" s="7"/>
-      <c r="H785" s="7"/>
-      <c r="I785" s="7"/>
-      <c r="J785" s="7"/>
-      <c r="K785" s="7"/>
-      <c r="L785" s="7"/>
-      <c r="M785" s="7"/>
-      <c r="N785" s="7"/>
-      <c r="O785" s="7" t="s">
+      <c r="O783" s="2" t="s">
         <v>1783</v>
       </c>
-      <c r="P785" s="7"/>
-      <c r="Q785" s="7"/>
-      <c r="R785" s="7"/>
-      <c r="S785" s="7"/>
-      <c r="T785" s="7"/>
-      <c r="U785" s="7"/>
-      <c r="V785" s="7"/>
-      <c r="W785" s="7"/>
-      <c r="X785" s="7"/>
-      <c r="Y785" s="7"/>
-    </row>
-    <row r="786" spans="1:25">
-      <c r="A786" s="7" t="s">
+    </row>
+    <row r="785" spans="1:15">
+      <c r="A785" s="2" t="s">
         <v>1784</v>
       </c>
-      <c r="B786" s="7" t="s">
-        <v>774</v>
-      </c>
-      <c r="D786" s="7"/>
-      <c r="E786" s="7"/>
-      <c r="F786" s="7"/>
-      <c r="G786" s="7"/>
-      <c r="H786" s="7"/>
-      <c r="I786" s="7"/>
-      <c r="J786" s="7"/>
-      <c r="K786" s="7"/>
-      <c r="L786" s="7"/>
-      <c r="M786" s="7"/>
-      <c r="N786" s="7"/>
-      <c r="O786" s="7" t="s">
+      <c r="B785" s="2" t="s">
         <v>1785</v>
       </c>
-      <c r="P786" s="7"/>
-      <c r="Q786" s="7"/>
-      <c r="R786" s="7"/>
-      <c r="S786" s="7"/>
-      <c r="T786" s="7"/>
-      <c r="U786" s="7"/>
-      <c r="V786" s="7"/>
-      <c r="W786" s="7"/>
-      <c r="X786" s="7"/>
-      <c r="Y786" s="7"/>
-    </row>
-    <row r="787" spans="1:25">
-      <c r="A787" s="7" t="s">
+      <c r="O785" s="2" t="s">
         <v>1786</v>
       </c>
-      <c r="B787" s="7" t="s">
+    </row>
+    <row r="786" spans="1:15">
+      <c r="A786" s="2" t="s">
         <v>1787</v>
       </c>
-      <c r="D787" s="7"/>
-      <c r="E787" s="7"/>
-      <c r="F787" s="7"/>
-      <c r="G787" s="7"/>
-      <c r="H787" s="7"/>
-      <c r="I787" s="7"/>
-      <c r="J787" s="7"/>
-      <c r="K787" s="7"/>
-      <c r="L787" s="7"/>
-      <c r="M787" s="7"/>
-      <c r="N787" s="7"/>
-      <c r="O787" s="7" t="s">
+      <c r="B786" s="2" t="s">
         <v>1788</v>
       </c>
-      <c r="P787" s="7"/>
-      <c r="Q787" s="7"/>
-      <c r="R787" s="7"/>
-      <c r="S787" s="7"/>
-      <c r="T787" s="7"/>
-      <c r="U787" s="7"/>
-      <c r="V787" s="7"/>
-      <c r="W787" s="7"/>
-      <c r="X787" s="7"/>
-      <c r="Y787" s="7"/>
+      <c r="O786" s="2" t="s">
+        <v>1789</v>
+      </c>
     </row>
     <row r="788" spans="1:25">
       <c r="A788" s="7" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="B788" s="7" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="D788" s="7"/>
       <c r="E788" s="7"/>
@@ -16043,7 +15989,7 @@
       <c r="M788" s="7"/>
       <c r="N788" s="7"/>
       <c r="O788" s="7" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="P788" s="7"/>
       <c r="Q788" s="7"/>
@@ -16058,10 +16004,10 @@
     </row>
     <row r="789" spans="1:25">
       <c r="A789" s="7" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="B789" s="7" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="D789" s="7"/>
       <c r="E789" s="7"/>
@@ -16075,7 +16021,7 @@
       <c r="M789" s="7"/>
       <c r="N789" s="7"/>
       <c r="O789" s="7" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="P789" s="7"/>
       <c r="Q789" s="7"/>
@@ -16088,190 +16034,316 @@
       <c r="X789" s="7"/>
       <c r="Y789" s="7"/>
     </row>
-    <row r="791" spans="1:15">
-      <c r="A791" s="2" t="s">
-        <v>1795</v>
-      </c>
-      <c r="B791" s="2" t="s">
+    <row r="790" spans="1:25">
+      <c r="A790" s="7" t="s">
         <v>1796</v>
       </c>
+      <c r="B790" s="7" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D790" s="7"/>
+      <c r="E790" s="7"/>
+      <c r="F790" s="7"/>
+      <c r="G790" s="7"/>
+      <c r="H790" s="7"/>
+      <c r="I790" s="7"/>
+      <c r="J790" s="7"/>
+      <c r="K790" s="7"/>
+      <c r="L790" s="7"/>
+      <c r="M790" s="7"/>
+      <c r="N790" s="7"/>
+      <c r="O790" s="7" t="s">
+        <v>1798</v>
+      </c>
+      <c r="P790" s="7"/>
+      <c r="Q790" s="7"/>
+      <c r="R790" s="7"/>
+      <c r="S790" s="7"/>
+      <c r="T790" s="7"/>
+      <c r="U790" s="7"/>
+      <c r="V790" s="7"/>
+      <c r="W790" s="7"/>
+      <c r="X790" s="7"/>
+      <c r="Y790" s="7"/>
+    </row>
+    <row r="791" spans="1:25">
+      <c r="A791" s="7" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B791" s="7" t="s">
+        <v>1800</v>
+      </c>
+      <c r="D791" s="7"/>
+      <c r="E791" s="7"/>
+      <c r="F791" s="7"/>
+      <c r="G791" s="7"/>
+      <c r="H791" s="7"/>
+      <c r="I791" s="7"/>
+      <c r="J791" s="7"/>
+      <c r="K791" s="7"/>
+      <c r="L791" s="7"/>
+      <c r="M791" s="7"/>
+      <c r="N791" s="7"/>
       <c r="O791" s="7" t="s">
-        <v>1797</v>
-      </c>
-    </row>
-    <row r="793" spans="1:15">
-      <c r="A793" s="2" t="s">
-        <v>1798</v>
-      </c>
-      <c r="B793" s="2" t="s">
-        <v>1799</v>
-      </c>
+        <v>1801</v>
+      </c>
+      <c r="P791" s="7"/>
+      <c r="Q791" s="7"/>
+      <c r="R791" s="7"/>
+      <c r="S791" s="7"/>
+      <c r="T791" s="7"/>
+      <c r="U791" s="7"/>
+      <c r="V791" s="7"/>
+      <c r="W791" s="7"/>
+      <c r="X791" s="7"/>
+      <c r="Y791" s="7"/>
+    </row>
+    <row r="792" spans="1:25">
+      <c r="A792" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="B792" s="7" t="s">
+        <v>783</v>
+      </c>
+      <c r="D792" s="7"/>
+      <c r="E792" s="7"/>
+      <c r="F792" s="7"/>
+      <c r="G792" s="7"/>
+      <c r="H792" s="7"/>
+      <c r="I792" s="7"/>
+      <c r="J792" s="7"/>
+      <c r="K792" s="7"/>
+      <c r="L792" s="7"/>
+      <c r="M792" s="7"/>
+      <c r="N792" s="7"/>
+      <c r="O792" s="7" t="s">
+        <v>1803</v>
+      </c>
+      <c r="P792" s="7"/>
+      <c r="Q792" s="7"/>
+      <c r="R792" s="7"/>
+      <c r="S792" s="7"/>
+      <c r="T792" s="7"/>
+      <c r="U792" s="7"/>
+      <c r="V792" s="7"/>
+      <c r="W792" s="7"/>
+      <c r="X792" s="7"/>
+      <c r="Y792" s="7"/>
+    </row>
+    <row r="793" spans="1:25">
+      <c r="A793" s="7" t="s">
+        <v>1804</v>
+      </c>
+      <c r="B793" s="7" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D793" s="7"/>
+      <c r="E793" s="7"/>
+      <c r="F793" s="7"/>
+      <c r="G793" s="7"/>
+      <c r="H793" s="7"/>
+      <c r="I793" s="7"/>
+      <c r="J793" s="7"/>
+      <c r="K793" s="7"/>
+      <c r="L793" s="7"/>
+      <c r="M793" s="7"/>
+      <c r="N793" s="7"/>
       <c r="O793" s="7" t="s">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="794" spans="1:15">
-      <c r="A794" s="2" t="s">
-        <v>1801</v>
-      </c>
-      <c r="B794" s="2" t="s">
-        <v>1802</v>
-      </c>
+        <v>1806</v>
+      </c>
+      <c r="P793" s="7"/>
+      <c r="Q793" s="7"/>
+      <c r="R793" s="7"/>
+      <c r="S793" s="7"/>
+      <c r="T793" s="7"/>
+      <c r="U793" s="7"/>
+      <c r="V793" s="7"/>
+      <c r="W793" s="7"/>
+      <c r="X793" s="7"/>
+      <c r="Y793" s="7"/>
+    </row>
+    <row r="794" spans="1:25">
+      <c r="A794" s="7" t="s">
+        <v>1807</v>
+      </c>
+      <c r="B794" s="7" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D794" s="7"/>
+      <c r="E794" s="7"/>
+      <c r="F794" s="7"/>
+      <c r="G794" s="7"/>
+      <c r="H794" s="7"/>
+      <c r="I794" s="7"/>
+      <c r="J794" s="7"/>
+      <c r="K794" s="7"/>
+      <c r="L794" s="7"/>
+      <c r="M794" s="7"/>
+      <c r="N794" s="7"/>
       <c r="O794" s="7" t="s">
-        <v>1803</v>
-      </c>
-    </row>
-    <row r="795" spans="1:15">
-      <c r="A795" s="2" t="s">
-        <v>1804</v>
-      </c>
-      <c r="B795" s="2" t="s">
-        <v>1805</v>
-      </c>
+        <v>1809</v>
+      </c>
+      <c r="P794" s="7"/>
+      <c r="Q794" s="7"/>
+      <c r="R794" s="7"/>
+      <c r="S794" s="7"/>
+      <c r="T794" s="7"/>
+      <c r="U794" s="7"/>
+      <c r="V794" s="7"/>
+      <c r="W794" s="7"/>
+      <c r="X794" s="7"/>
+      <c r="Y794" s="7"/>
+    </row>
+    <row r="795" spans="1:25">
+      <c r="A795" s="7" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B795" s="7" t="s">
+        <v>1811</v>
+      </c>
+      <c r="D795" s="7"/>
+      <c r="E795" s="7"/>
+      <c r="F795" s="7"/>
+      <c r="G795" s="7"/>
+      <c r="H795" s="7"/>
+      <c r="I795" s="7"/>
+      <c r="J795" s="7"/>
+      <c r="K795" s="7"/>
+      <c r="L795" s="7"/>
+      <c r="M795" s="7"/>
+      <c r="N795" s="7"/>
       <c r="O795" s="7" t="s">
-        <v>1806</v>
-      </c>
+        <v>1812</v>
+      </c>
+      <c r="P795" s="7"/>
+      <c r="Q795" s="7"/>
+      <c r="R795" s="7"/>
+      <c r="S795" s="7"/>
+      <c r="T795" s="7"/>
+      <c r="U795" s="7"/>
+      <c r="V795" s="7"/>
+      <c r="W795" s="7"/>
+      <c r="X795" s="7"/>
+      <c r="Y795" s="7"/>
     </row>
     <row r="797" spans="1:15">
       <c r="A797" s="2" t="s">
-        <v>1807</v>
+        <v>1813</v>
       </c>
       <c r="B797" s="2" t="s">
-        <v>1808</v>
-      </c>
-      <c r="O797" s="2" t="s">
-        <v>1809</v>
-      </c>
-    </row>
-    <row r="798" spans="1:15">
-      <c r="A798" s="2" t="s">
-        <v>1810</v>
-      </c>
-      <c r="B798" s="2" t="s">
-        <v>1811</v>
-      </c>
-      <c r="O798" s="2" t="s">
-        <v>1812</v>
+        <v>1814</v>
+      </c>
+      <c r="O797" s="7" t="s">
+        <v>1815</v>
       </c>
     </row>
     <row r="799" spans="1:15">
       <c r="A799" s="2" t="s">
-        <v>1813</v>
+        <v>1816</v>
       </c>
       <c r="B799" s="2" t="s">
-        <v>1814</v>
-      </c>
-      <c r="O799" s="2" t="s">
-        <v>1815</v>
+        <v>1817</v>
+      </c>
+      <c r="O799" s="7" t="s">
+        <v>1818</v>
       </c>
     </row>
     <row r="800" spans="1:15">
       <c r="A800" s="2" t="s">
-        <v>1816</v>
+        <v>1819</v>
       </c>
       <c r="B800" s="2" t="s">
-        <v>1817</v>
-      </c>
-      <c r="O800" s="2" t="s">
-        <v>1818</v>
-      </c>
-    </row>
-    <row r="802" spans="1:15">
-      <c r="A802" s="2" t="s">
-        <v>1819</v>
-      </c>
-      <c r="B802" s="2" t="s">
         <v>1820</v>
       </c>
-      <c r="O802" s="2" t="s">
+      <c r="O800" s="7" t="s">
         <v>1821</v>
+      </c>
+    </row>
+    <row r="801" spans="1:15">
+      <c r="A801" s="2" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B801" s="2" t="s">
+        <v>1823</v>
+      </c>
+      <c r="O801" s="7" t="s">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="803" spans="1:15">
+      <c r="A803" s="2" t="s">
+        <v>1825</v>
+      </c>
+      <c r="B803" s="2" t="s">
+        <v>1826</v>
+      </c>
+      <c r="O803" s="2" t="s">
+        <v>1827</v>
       </c>
     </row>
     <row r="804" spans="1:15">
       <c r="A804" s="2" t="s">
-        <v>1822</v>
+        <v>1828</v>
       </c>
       <c r="B804" s="2" t="s">
-        <v>1823</v>
+        <v>1829</v>
       </c>
       <c r="O804" s="2" t="s">
-        <v>1824</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="805" spans="1:15">
       <c r="A805" s="2" t="s">
-        <v>1825</v>
+        <v>1831</v>
       </c>
       <c r="B805" s="2" t="s">
-        <v>1826</v>
+        <v>1832</v>
       </c>
       <c r="O805" s="2" t="s">
-        <v>1827</v>
-      </c>
-    </row>
-    <row r="807" spans="1:15">
-      <c r="A807" s="7" t="s">
-        <v>1828</v>
-      </c>
-      <c r="B807" s="7" t="s">
-        <v>1829</v>
-      </c>
-      <c r="O807" s="7" t="s">
-        <v>1830</v>
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="806" spans="1:15">
+      <c r="A806" s="2" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B806" s="2" t="s">
+        <v>1835</v>
+      </c>
+      <c r="O806" s="2" t="s">
+        <v>1836</v>
       </c>
     </row>
     <row r="808" spans="1:15">
-      <c r="A808" s="7" t="s">
-        <v>1831</v>
-      </c>
-      <c r="B808" s="7" t="s">
-        <v>1832</v>
-      </c>
-      <c r="O808" s="7" t="s">
-        <v>1833</v>
-      </c>
-    </row>
-    <row r="809" spans="1:15">
-      <c r="A809" s="7" t="s">
-        <v>1834</v>
-      </c>
-      <c r="B809" s="7" t="s">
-        <v>1835</v>
-      </c>
-      <c r="O809" s="7" t="s">
-        <v>1836</v>
+      <c r="A808" s="2" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B808" s="2" t="s">
+        <v>1838</v>
+      </c>
+      <c r="O808" s="2" t="s">
+        <v>1839</v>
       </c>
     </row>
     <row r="810" spans="1:15">
-      <c r="A810" s="7" t="s">
-        <v>1837</v>
-      </c>
-      <c r="B810" s="7" t="s">
-        <v>1838</v>
-      </c>
-      <c r="O810" s="7" t="s">
-        <v>1839</v>
+      <c r="A810" s="2" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B810" s="2" t="s">
+        <v>1841</v>
+      </c>
+      <c r="O810" s="2" t="s">
+        <v>1842</v>
       </c>
     </row>
     <row r="811" spans="1:15">
-      <c r="A811" s="7" t="s">
-        <v>1840</v>
-      </c>
-      <c r="B811" s="7" t="s">
-        <v>1841</v>
-      </c>
-      <c r="O811" s="7" t="s">
-        <v>1842</v>
-      </c>
-    </row>
-    <row r="812" spans="1:15">
-      <c r="A812" s="7" t="s">
+      <c r="A811" s="2" t="s">
         <v>1843</v>
       </c>
-      <c r="B812" s="7" t="s">
+      <c r="B811" s="2" t="s">
         <v>1844</v>
       </c>
-      <c r="O812" s="7" t="s">
+      <c r="O811" s="2" t="s">
         <v>1845</v>
       </c>
     </row>
@@ -16302,86 +16374,86 @@
         <v>1852</v>
       </c>
       <c r="B815" s="7" t="s">
-        <v>1829</v>
+        <v>1853</v>
       </c>
       <c r="O815" s="7" t="s">
-        <v>1830</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="816" spans="1:15">
       <c r="A816" s="7" t="s">
-        <v>1853</v>
+        <v>1855</v>
       </c>
       <c r="B816" s="7" t="s">
-        <v>1854</v>
+        <v>1856</v>
       </c>
       <c r="O816" s="7" t="s">
-        <v>1855</v>
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="817" spans="1:15">
+      <c r="A817" s="7" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B817" s="7" t="s">
+        <v>1859</v>
+      </c>
+      <c r="O817" s="7" t="s">
+        <v>1860</v>
       </c>
     </row>
     <row r="818" spans="1:15">
       <c r="A818" s="7" t="s">
-        <v>1856</v>
+        <v>1861</v>
       </c>
       <c r="B818" s="7" t="s">
-        <v>1857</v>
+        <v>1862</v>
       </c>
       <c r="O818" s="7" t="s">
-        <v>1858</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="819" spans="1:15">
       <c r="A819" s="7" t="s">
-        <v>1859</v>
+        <v>1864</v>
       </c>
       <c r="B819" s="7" t="s">
-        <v>1860</v>
+        <v>1865</v>
       </c>
       <c r="O819" s="7" t="s">
-        <v>1861</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="820" spans="1:15">
       <c r="A820" s="7" t="s">
-        <v>1862</v>
+        <v>1867</v>
       </c>
       <c r="B820" s="7" t="s">
-        <v>1863</v>
+        <v>1868</v>
       </c>
       <c r="O820" s="7" t="s">
-        <v>1864</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="821" spans="1:15">
       <c r="A821" s="7" t="s">
-        <v>1865</v>
+        <v>1870</v>
       </c>
       <c r="B821" s="7" t="s">
-        <v>1866</v>
+        <v>1847</v>
       </c>
       <c r="O821" s="7" t="s">
-        <v>1867</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="822" spans="1:15">
       <c r="A822" s="7" t="s">
-        <v>1868</v>
+        <v>1871</v>
       </c>
       <c r="B822" s="7" t="s">
-        <v>1869</v>
+        <v>1872</v>
       </c>
       <c r="O822" s="7" t="s">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="823" spans="1:15">
-      <c r="A823" s="7" t="s">
-        <v>1871</v>
-      </c>
-      <c r="B823" s="7" t="s">
-        <v>1872</v>
-      </c>
-      <c r="O823" s="7" t="s">
         <v>1873</v>
       </c>
     </row>
@@ -16440,124 +16512,124 @@
         <v>1888</v>
       </c>
     </row>
+    <row r="829" spans="1:15">
+      <c r="A829" s="7" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B829" s="7" t="s">
+        <v>1890</v>
+      </c>
+      <c r="O829" s="7" t="s">
+        <v>1891</v>
+      </c>
+    </row>
     <row r="830" spans="1:15">
-      <c r="A830" s="2" t="s">
-        <v>1889</v>
-      </c>
-      <c r="B830" s="2" t="s">
-        <v>1890</v>
-      </c>
-      <c r="O830" s="2" t="s">
-        <v>1891</v>
+      <c r="A830" s="7" t="s">
+        <v>1892</v>
+      </c>
+      <c r="B830" s="7" t="s">
+        <v>1893</v>
+      </c>
+      <c r="O830" s="7" t="s">
+        <v>1894</v>
       </c>
     </row>
     <row r="831" spans="1:15">
-      <c r="A831" s="2" t="s">
-        <v>1892</v>
-      </c>
-      <c r="B831" s="2" t="s">
-        <v>1893</v>
-      </c>
-      <c r="O831" s="2" t="s">
-        <v>1894</v>
+      <c r="A831" s="7" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B831" s="7" t="s">
+        <v>1896</v>
+      </c>
+      <c r="O831" s="7" t="s">
+        <v>1897</v>
       </c>
     </row>
     <row r="832" spans="1:15">
-      <c r="A832" s="2" t="s">
-        <v>1895</v>
-      </c>
-      <c r="B832" s="2" t="s">
-        <v>1896</v>
-      </c>
-      <c r="O832" s="2" t="s">
-        <v>1897</v>
+      <c r="A832" s="7" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B832" s="7" t="s">
+        <v>1899</v>
+      </c>
+      <c r="O832" s="7" t="s">
+        <v>1900</v>
       </c>
     </row>
     <row r="833" spans="1:15">
-      <c r="A833" s="2" t="s">
-        <v>1898</v>
-      </c>
-      <c r="B833" s="2" t="s">
-        <v>1899</v>
-      </c>
-      <c r="O833" s="2" t="s">
-        <v>1900</v>
+      <c r="A833" s="7" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B833" s="7" t="s">
+        <v>1902</v>
+      </c>
+      <c r="O833" s="7" t="s">
+        <v>1903</v>
       </c>
     </row>
     <row r="834" spans="1:15">
-      <c r="A834" s="2" t="s">
-        <v>1901</v>
-      </c>
-      <c r="B834" s="2" t="s">
-        <v>1902</v>
-      </c>
-      <c r="O834" s="2" t="s">
-        <v>1903</v>
+      <c r="A834" s="7" t="s">
+        <v>1904</v>
+      </c>
+      <c r="B834" s="7" t="s">
+        <v>1905</v>
+      </c>
+      <c r="O834" s="7" t="s">
+        <v>1906</v>
       </c>
     </row>
     <row r="836" spans="1:15">
-      <c r="A836" s="7" t="s">
-        <v>1904</v>
-      </c>
-      <c r="B836" s="7" t="s">
-        <v>1905</v>
-      </c>
-      <c r="O836" s="7" t="s">
-        <v>1906</v>
+      <c r="A836" s="2" t="s">
+        <v>1907</v>
+      </c>
+      <c r="B836" s="2" t="s">
+        <v>1908</v>
+      </c>
+      <c r="O836" s="2" t="s">
+        <v>1909</v>
       </c>
     </row>
     <row r="837" spans="1:15">
-      <c r="A837" s="7" t="s">
-        <v>1907</v>
-      </c>
-      <c r="B837" s="7" t="s">
-        <v>1908</v>
-      </c>
-      <c r="O837" s="7" t="s">
-        <v>1909</v>
+      <c r="A837" s="2" t="s">
+        <v>1910</v>
+      </c>
+      <c r="B837" s="2" t="s">
+        <v>1911</v>
+      </c>
+      <c r="O837" s="2" t="s">
+        <v>1912</v>
       </c>
     </row>
     <row r="838" spans="1:15">
-      <c r="A838" s="7" t="s">
-        <v>1910</v>
-      </c>
-      <c r="B838" s="7" t="s">
-        <v>1911</v>
-      </c>
-      <c r="O838" s="7" t="s">
-        <v>1912</v>
+      <c r="A838" s="2" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B838" s="2" t="s">
+        <v>1914</v>
+      </c>
+      <c r="O838" s="2" t="s">
+        <v>1915</v>
       </c>
     </row>
     <row r="839" spans="1:15">
-      <c r="A839" s="7" t="s">
-        <v>1913</v>
-      </c>
-      <c r="B839" s="7" t="s">
-        <v>1914</v>
-      </c>
-      <c r="O839" s="7" t="s">
-        <v>1915</v>
+      <c r="A839" s="2" t="s">
+        <v>1916</v>
+      </c>
+      <c r="B839" s="2" t="s">
+        <v>1917</v>
+      </c>
+      <c r="O839" s="2" t="s">
+        <v>1918</v>
       </c>
     </row>
     <row r="840" spans="1:15">
-      <c r="A840" s="7" t="s">
-        <v>1916</v>
-      </c>
-      <c r="B840" s="7" t="s">
-        <v>1917</v>
-      </c>
-      <c r="O840" s="7" t="s">
-        <v>1918</v>
-      </c>
-    </row>
-    <row r="841" spans="1:15">
-      <c r="A841" s="7" t="s">
+      <c r="A840" s="2" t="s">
         <v>1919</v>
       </c>
-      <c r="B841" s="7" t="s">
+      <c r="B840" s="2" t="s">
         <v>1920</v>
       </c>
-      <c r="O841" s="7" t="s">
+      <c r="O840" s="2" t="s">
         <v>1921</v>
       </c>
     </row>
@@ -16594,362 +16666,428 @@
         <v>1930</v>
       </c>
     </row>
+    <row r="845" spans="1:15">
+      <c r="A845" s="7" t="s">
+        <v>1931</v>
+      </c>
+      <c r="B845" s="7" t="s">
+        <v>1932</v>
+      </c>
+      <c r="O845" s="7" t="s">
+        <v>1933</v>
+      </c>
+    </row>
     <row r="846" spans="1:15">
       <c r="A846" s="7" t="s">
-        <v>1931</v>
+        <v>1934</v>
       </c>
       <c r="B846" s="7" t="s">
-        <v>1932</v>
+        <v>1935</v>
       </c>
       <c r="O846" s="7" t="s">
-        <v>1933</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="847" spans="1:15">
       <c r="A847" s="7" t="s">
-        <v>1934</v>
+        <v>1937</v>
       </c>
       <c r="B847" s="7" t="s">
-        <v>1935</v>
+        <v>1938</v>
       </c>
       <c r="O847" s="7" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="848" spans="1:15">
       <c r="A848" s="7" t="s">
-        <v>1937</v>
+        <v>1940</v>
       </c>
       <c r="B848" s="7" t="s">
-        <v>1938</v>
+        <v>1941</v>
       </c>
       <c r="O848" s="7" t="s">
-        <v>1939</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="849" spans="1:15">
       <c r="A849" s="7" t="s">
-        <v>1940</v>
+        <v>1943</v>
       </c>
       <c r="B849" s="7" t="s">
-        <v>1941</v>
+        <v>1944</v>
       </c>
       <c r="O849" s="7" t="s">
-        <v>1942</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="850" spans="1:15">
       <c r="A850" s="7" t="s">
-        <v>1943</v>
+        <v>1946</v>
       </c>
       <c r="B850" s="7" t="s">
-        <v>1944</v>
+        <v>1947</v>
       </c>
       <c r="O850" s="7" t="s">
-        <v>1945</v>
-      </c>
-    </row>
-    <row r="851" spans="1:2">
-      <c r="A851" s="7"/>
-      <c r="B851" s="7"/>
+        <v>1948</v>
+      </c>
     </row>
     <row r="852" spans="1:15">
       <c r="A852" s="7" t="s">
-        <v>1946</v>
+        <v>1949</v>
       </c>
       <c r="B852" s="7" t="s">
-        <v>1947</v>
+        <v>1950</v>
       </c>
       <c r="O852" s="7" t="s">
-        <v>1948</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="853" spans="1:15">
       <c r="A853" s="7" t="s">
-        <v>1949</v>
+        <v>1952</v>
       </c>
       <c r="B853" s="7" t="s">
-        <v>774</v>
+        <v>1953</v>
       </c>
       <c r="O853" s="7" t="s">
-        <v>1785</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="854" spans="1:15">
       <c r="A854" s="7" t="s">
-        <v>1950</v>
+        <v>1955</v>
       </c>
       <c r="B854" s="7" t="s">
-        <v>1787</v>
+        <v>1956</v>
       </c>
       <c r="O854" s="7" t="s">
-        <v>1788</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="855" spans="1:15">
       <c r="A855" s="7" t="s">
-        <v>1951</v>
+        <v>1958</v>
       </c>
       <c r="B855" s="7" t="s">
-        <v>1952</v>
+        <v>1959</v>
       </c>
       <c r="O855" s="7" t="s">
-        <v>1953</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="856" spans="1:15">
       <c r="A856" s="7" t="s">
-        <v>1954</v>
+        <v>1961</v>
       </c>
       <c r="B856" s="7" t="s">
-        <v>1955</v>
+        <v>1962</v>
       </c>
       <c r="O856" s="7" t="s">
-        <v>1956</v>
-      </c>
-    </row>
-    <row r="857" spans="1:15">
-      <c r="A857" s="7" t="s">
-        <v>1957</v>
-      </c>
-      <c r="B857" s="7" t="s">
-        <v>1958</v>
-      </c>
-      <c r="O857" s="7" t="s">
-        <v>1956</v>
-      </c>
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="857" spans="1:2">
+      <c r="A857" s="7"/>
+      <c r="B857" s="7"/>
     </row>
     <row r="858" spans="1:15">
       <c r="A858" s="7" t="s">
-        <v>1959</v>
+        <v>1964</v>
       </c>
       <c r="B858" s="7" t="s">
-        <v>1960</v>
+        <v>1965</v>
       </c>
       <c r="O858" s="7" t="s">
-        <v>1961</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="859" spans="1:15">
       <c r="A859" s="7" t="s">
-        <v>1962</v>
+        <v>1967</v>
       </c>
       <c r="B859" s="7" t="s">
-        <v>1963</v>
+        <v>783</v>
       </c>
       <c r="O859" s="7" t="s">
-        <v>1961</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="860" spans="1:15">
       <c r="A860" s="7" t="s">
-        <v>1964</v>
+        <v>1968</v>
       </c>
       <c r="B860" s="7" t="s">
-        <v>1965</v>
+        <v>1805</v>
       </c>
       <c r="O860" s="7" t="s">
-        <v>1966</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="861" spans="1:15">
       <c r="A861" s="7" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="B861" s="7" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="O861" s="7" t="s">
-        <v>1966</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="862" spans="1:15">
       <c r="A862" s="7" t="s">
-        <v>1969</v>
+        <v>1972</v>
       </c>
       <c r="B862" s="7" t="s">
-        <v>1970</v>
+        <v>1973</v>
       </c>
       <c r="O862" s="7" t="s">
-        <v>1971</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="863" spans="1:15">
       <c r="A863" s="7" t="s">
-        <v>1972</v>
+        <v>1975</v>
       </c>
       <c r="B863" s="7" t="s">
-        <v>1973</v>
+        <v>1976</v>
       </c>
       <c r="O863" s="7" t="s">
-        <v>1971</v>
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="864" spans="1:15">
+      <c r="A864" s="7" t="s">
+        <v>1977</v>
+      </c>
+      <c r="B864" s="7" t="s">
+        <v>1978</v>
+      </c>
+      <c r="O864" s="7" t="s">
+        <v>1979</v>
       </c>
     </row>
     <row r="865" spans="1:15">
-      <c r="A865" s="2" t="s">
-        <v>1974</v>
-      </c>
-      <c r="B865" s="2" t="s">
-        <v>1975</v>
-      </c>
-      <c r="O865" s="2" t="s">
-        <v>1976</v>
+      <c r="A865" s="7" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B865" s="7" t="s">
+        <v>1981</v>
+      </c>
+      <c r="O865" s="7" t="s">
+        <v>1979</v>
       </c>
     </row>
     <row r="866" spans="1:15">
-      <c r="A866" s="2" t="s">
-        <v>1977</v>
-      </c>
-      <c r="B866" s="2" t="s">
-        <v>1978</v>
-      </c>
-      <c r="O866" s="2" t="s">
-        <v>1979</v>
+      <c r="A866" s="7" t="s">
+        <v>1982</v>
+      </c>
+      <c r="B866" s="7" t="s">
+        <v>1983</v>
+      </c>
+      <c r="O866" s="7" t="s">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="867" spans="1:15">
+      <c r="A867" s="7" t="s">
+        <v>1985</v>
+      </c>
+      <c r="B867" s="7" t="s">
+        <v>1986</v>
+      </c>
+      <c r="O867" s="7" t="s">
+        <v>1984</v>
       </c>
     </row>
     <row r="868" spans="1:15">
-      <c r="A868" s="2" t="s">
-        <v>1980</v>
-      </c>
-      <c r="B868" s="2" t="s">
-        <v>1981</v>
-      </c>
-      <c r="O868" s="2" t="s">
-        <v>1982</v>
+      <c r="A868" s="7" t="s">
+        <v>1987</v>
+      </c>
+      <c r="B868" s="7" t="s">
+        <v>1988</v>
+      </c>
+      <c r="O868" s="7" t="s">
+        <v>1989</v>
       </c>
     </row>
     <row r="869" spans="1:15">
-      <c r="A869" s="2" t="s">
-        <v>1983</v>
-      </c>
-      <c r="B869" s="2" t="s">
-        <v>1984</v>
-      </c>
-      <c r="O869" s="2" t="s">
-        <v>1985</v>
-      </c>
-    </row>
-    <row r="870" spans="1:15">
-      <c r="A870" s="2" t="s">
-        <v>1986</v>
-      </c>
-      <c r="B870" s="2" t="s">
-        <v>1987</v>
-      </c>
-      <c r="O870" s="2" t="s">
-        <v>1988</v>
+      <c r="A869" s="7" t="s">
+        <v>1990</v>
+      </c>
+      <c r="B869" s="7" t="s">
+        <v>1991</v>
+      </c>
+      <c r="O869" s="7" t="s">
+        <v>1989</v>
       </c>
     </row>
     <row r="871" spans="1:15">
       <c r="A871" s="2" t="s">
-        <v>1989</v>
+        <v>1992</v>
       </c>
       <c r="B871" s="2" t="s">
-        <v>1990</v>
+        <v>1993</v>
       </c>
       <c r="O871" s="2" t="s">
-        <v>1991</v>
-      </c>
-    </row>
-    <row r="873" spans="1:15">
-      <c r="A873" s="2" t="s">
-        <v>1992</v>
-      </c>
-      <c r="B873" s="2" t="s">
-        <v>1993</v>
-      </c>
-      <c r="O873" s="2" t="s">
         <v>1994</v>
+      </c>
+    </row>
+    <row r="872" spans="1:15">
+      <c r="A872" s="2" t="s">
+        <v>1995</v>
+      </c>
+      <c r="B872" s="2" t="s">
+        <v>1996</v>
+      </c>
+      <c r="O872" s="2" t="s">
+        <v>1997</v>
       </c>
     </row>
     <row r="874" spans="1:15">
       <c r="A874" s="2" t="s">
-        <v>1995</v>
+        <v>1998</v>
       </c>
       <c r="B874" s="2" t="s">
-        <v>1996</v>
+        <v>1999</v>
       </c>
       <c r="O874" s="2" t="s">
-        <v>1997</v>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="875" spans="1:15">
+      <c r="A875" s="2" t="s">
+        <v>2001</v>
+      </c>
+      <c r="B875" s="2" t="s">
+        <v>2002</v>
+      </c>
+      <c r="O875" s="2" t="s">
+        <v>2003</v>
       </c>
     </row>
     <row r="876" spans="1:15">
       <c r="A876" s="2" t="s">
-        <v>1998</v>
+        <v>2004</v>
       </c>
       <c r="B876" s="2" t="s">
-        <v>1999</v>
+        <v>2005</v>
       </c>
       <c r="O876" s="2" t="s">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="878" spans="1:15">
-      <c r="A878" s="2" t="s">
-        <v>2001</v>
-      </c>
-      <c r="B878" s="2" t="s">
-        <v>2002</v>
-      </c>
-      <c r="O878" s="2" t="s">
-        <v>2003</v>
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="877" spans="1:15">
+      <c r="A877" s="2" t="s">
+        <v>2007</v>
+      </c>
+      <c r="B877" s="2" t="s">
+        <v>2008</v>
+      </c>
+      <c r="O877" s="2" t="s">
+        <v>2009</v>
       </c>
     </row>
     <row r="879" spans="1:15">
       <c r="A879" s="2" t="s">
-        <v>2004</v>
+        <v>2010</v>
       </c>
       <c r="B879" s="2" t="s">
-        <v>2005</v>
+        <v>2011</v>
       </c>
       <c r="O879" s="2" t="s">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="881" spans="1:15">
-      <c r="A881" s="2" t="s">
-        <v>2007</v>
-      </c>
-      <c r="B881" s="2" t="s">
-        <v>2008</v>
-      </c>
-      <c r="O881" s="2" t="s">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="882" spans="1:2">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="880" spans="1:15">
+      <c r="A880" s="2" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B880" s="2" t="s">
+        <v>2014</v>
+      </c>
+      <c r="O880" s="2" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="882" spans="1:15">
       <c r="A882" s="2" t="s">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="B882" s="2" t="s">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="883" spans="1:2">
-      <c r="A883" s="2" t="s">
-        <v>2012</v>
-      </c>
-      <c r="B883" s="2" t="s">
+        <v>2017</v>
+      </c>
+      <c r="O882" s="2" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="884" spans="1:15">
+      <c r="A884" s="2" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B884" s="2" t="s">
+        <v>2020</v>
+      </c>
+      <c r="O884" s="2" t="s">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="885" spans="1:15">
+      <c r="A885" s="2" t="s">
+        <v>2022</v>
+      </c>
+      <c r="B885" s="2" t="s">
+        <v>2023</v>
+      </c>
+      <c r="O885" s="2" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="887" spans="1:15">
+      <c r="A887" s="2" t="s">
+        <v>2025</v>
+      </c>
+      <c r="B887" s="2" t="s">
+        <v>2026</v>
+      </c>
+      <c r="O887" s="2" t="s">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="888" spans="1:2">
+      <c r="A888" s="2" t="s">
+        <v>2028</v>
+      </c>
+      <c r="B888" s="2" t="s">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="889" spans="1:2">
+      <c r="A889" s="2" t="s">
+        <v>2030</v>
+      </c>
+      <c r="B889" s="2" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="884" spans="1:2">
-      <c r="A884" s="2" t="s">
-        <v>2013</v>
-      </c>
-      <c r="B884" s="2" t="s">
+    <row r="890" spans="1:2">
+      <c r="A890" s="2" t="s">
+        <v>2031</v>
+      </c>
+      <c r="B890" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="886" spans="1:15">
-      <c r="A886" s="2" t="s">
-        <v>2014</v>
-      </c>
-      <c r="B886" s="2" t="s">
-        <v>2015</v>
-      </c>
-      <c r="O886" s="2" t="s">
-        <v>2016</v>
+    <row r="892" spans="1:15">
+      <c r="A892" s="2" t="s">
+        <v>2032</v>
+      </c>
+      <c r="B892" s="2" t="s">
+        <v>2033</v>
+      </c>
+      <c r="O892" s="2" t="s">
+        <v>2034</v>
       </c>
     </row>
   </sheetData>
@@ -16963,7 +17101,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q44"/>
+  <dimension ref="A1:Q46"/>
   <sheetFormatPr defaultColWidth="33" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="34.8571428571429" style="2" customWidth="1"/>
@@ -17038,321 +17176,321 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>2017</v>
+        <v>2035</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>2018</v>
+        <v>2036</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>2019</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="2" t="s">
-        <v>2020</v>
+        <v>2038</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>2021</v>
+        <v>2039</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>2022</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="2" t="s">
-        <v>2023</v>
+        <v>2041</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>2024</v>
+        <v>2042</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>2025</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="2" t="s">
-        <v>2026</v>
+        <v>2044</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>2027</v>
+        <v>2045</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>2028</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="2" t="s">
-        <v>2029</v>
+        <v>2047</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>2030</v>
+        <v>2048</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>2031</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="2" t="s">
-        <v>2032</v>
+        <v>2050</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>2033</v>
+        <v>2051</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>2034</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="2" t="s">
-        <v>2035</v>
+        <v>2053</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>2036</v>
+        <v>2054</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>2037</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="2" t="s">
-        <v>2038</v>
+        <v>2056</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>2039</v>
+        <v>2057</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>2040</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="2" t="s">
-        <v>2041</v>
+        <v>2059</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>2042</v>
+        <v>2060</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>2043</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="2" t="s">
-        <v>2044</v>
+        <v>2062</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>2045</v>
+        <v>2063</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>2046</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="2" t="s">
-        <v>2047</v>
+        <v>2065</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>2048</v>
+        <v>2066</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>2049</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="2" t="s">
-        <v>2050</v>
+        <v>2068</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>2051</v>
+        <v>2069</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>2052</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="2" t="s">
-        <v>2053</v>
+        <v>2071</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>2054</v>
+        <v>2072</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>2055</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="2" t="s">
-        <v>2056</v>
+        <v>2074</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>2057</v>
+        <v>2075</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>2058</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="2" t="s">
-        <v>2059</v>
+        <v>2077</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>2060</v>
+        <v>2078</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>2061</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="2" t="s">
-        <v>2062</v>
+        <v>2080</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>546</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>2063</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="2" t="s">
-        <v>2064</v>
+        <v>2082</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>2065</v>
+        <v>2083</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>2066</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="2" t="s">
-        <v>2067</v>
+        <v>2085</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>2068</v>
+        <v>2086</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>2069</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="2" t="s">
-        <v>2070</v>
+        <v>2088</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>2071</v>
+        <v>2089</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>2072</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="2" t="s">
-        <v>2073</v>
+        <v>2091</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>2074</v>
+        <v>2092</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>2075</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="2" t="s">
-        <v>2076</v>
+        <v>2094</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>2077</v>
+        <v>2095</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>2078</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="2" t="s">
-        <v>2079</v>
+        <v>2097</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>2080</v>
+        <v>2098</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>2081</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="2" t="s">
-        <v>2082</v>
+        <v>2100</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>2083</v>
+        <v>2101</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>2084</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="2" t="s">
-        <v>2085</v>
+        <v>2103</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>2086</v>
+        <v>2104</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>2087</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="2" t="s">
-        <v>2088</v>
+        <v>2106</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>2089</v>
+        <v>2107</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>2090</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="2" t="s">
-        <v>2091</v>
+        <v>2109</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>2092</v>
+        <v>2110</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>2093</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="2" t="s">
-        <v>2094</v>
+        <v>2112</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>2095</v>
+        <v>2113</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>2096</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="2" t="s">
-        <v>2097</v>
+        <v>2115</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>2098</v>
+        <v>2116</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>2099</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="2" t="s">
-        <v>2100</v>
+        <v>2118</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>2101</v>
+        <v>2119</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>2102</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="31" spans="1:15">
@@ -17360,153 +17498,175 @@
         <v>687</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>2103</v>
+        <v>2121</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>2104</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="2" t="s">
-        <v>2105</v>
+        <v>2123</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>2106</v>
+        <v>2124</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>2107</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="2" t="s">
-        <v>2108</v>
+        <v>2126</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>2109</v>
+        <v>2127</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>2110</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="34" spans="1:15">
       <c r="A34" s="2" t="s">
-        <v>2111</v>
+        <v>2129</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>2112</v>
+        <v>2130</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>2113</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="35" spans="1:15">
       <c r="A35" s="2" t="s">
-        <v>2114</v>
+        <v>2132</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>2115</v>
+        <v>2133</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>2116</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="36" spans="1:15">
       <c r="A36" s="2" t="s">
-        <v>2117</v>
+        <v>2135</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>2118</v>
+        <v>2136</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>2119</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="37" spans="1:15">
       <c r="A37" s="2" t="s">
-        <v>2120</v>
+        <v>2138</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>2121</v>
+        <v>2139</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>2122</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="38" spans="1:15">
       <c r="A38" s="2" t="s">
-        <v>2123</v>
+        <v>2141</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>2065</v>
+        <v>2083</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>2124</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="39" spans="1:15">
       <c r="A39" s="2" t="s">
-        <v>2125</v>
+        <v>2143</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>2126</v>
+        <v>2144</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>2127</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="40" spans="1:15">
       <c r="A40" s="2" t="s">
-        <v>2128</v>
+        <v>2146</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>2129</v>
+        <v>2147</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>2130</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="41" spans="1:15">
       <c r="A41" s="2" t="s">
-        <v>2131</v>
+        <v>2149</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>2132</v>
+        <v>2150</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>2133</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="42" spans="1:15">
       <c r="A42" s="2" t="s">
-        <v>2134</v>
+        <v>2152</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>2135</v>
+        <v>2153</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>2136</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="43" spans="1:15">
       <c r="A43" s="2" t="s">
-        <v>2137</v>
+        <v>2155</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>2138</v>
+        <v>2156</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>2139</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="44" spans="1:15">
       <c r="A44" s="2" t="s">
-        <v>2140</v>
+        <v>2158</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>2141</v>
+        <v>2159</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>2142</v>
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45" s="2" t="s">
+        <v>2161</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>2162</v>
+      </c>
+      <c r="O45" s="2" t="s">
+        <v>2163</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" s="2" t="s">
+        <v>2164</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>2165</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>2166</v>
       </c>
     </row>
   </sheetData>
@@ -17581,10 +17741,10 @@
     </row>
     <row r="2" customFormat="1" ht="28.5" spans="1:17">
       <c r="A2" s="1" t="s">
-        <v>2143</v>
+        <v>2167</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>2144</v>
+        <v>2168</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -17599,17 +17759,17 @@
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
       <c r="O2" s="6" t="s">
-        <v>2145</v>
+        <v>2169</v>
       </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
     <row r="3" ht="57" spans="1:17">
       <c r="A3" s="1" t="s">
-        <v>2146</v>
+        <v>2170</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>2147</v>
+        <v>2171</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -17624,17 +17784,17 @@
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="6" t="s">
-        <v>2148</v>
+        <v>2172</v>
       </c>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
     <row r="4" ht="42.75" spans="1:17">
       <c r="A4" s="1" t="s">
-        <v>2149</v>
+        <v>2173</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>2150</v>
+        <v>2174</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -17649,17 +17809,17 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="6" t="s">
-        <v>2151</v>
+        <v>2175</v>
       </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
     <row r="5" ht="71.25" spans="1:17">
       <c r="A5" s="1" t="s">
-        <v>2152</v>
+        <v>2176</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>2153</v>
+        <v>2177</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -17674,17 +17834,17 @@
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="6" t="s">
-        <v>2154</v>
+        <v>2178</v>
       </c>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
     </row>
     <row r="6" ht="42.75" spans="1:17">
       <c r="A6" s="1" t="s">
-        <v>2155</v>
+        <v>2179</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>2156</v>
+        <v>2180</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -17699,17 +17859,17 @@
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="6" t="s">
-        <v>2157</v>
+        <v>2181</v>
       </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
     </row>
     <row r="7" ht="57" spans="1:17">
       <c r="A7" s="1" t="s">
-        <v>2158</v>
+        <v>2182</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>2159</v>
+        <v>2183</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -17724,17 +17884,17 @@
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="6" t="s">
-        <v>2160</v>
+        <v>2184</v>
       </c>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="1" t="s">
-        <v>2161</v>
+        <v>2185</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>2162</v>
+        <v>2186</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -17749,7 +17909,7 @@
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1" t="s">
-        <v>2163</v>
+        <v>2187</v>
       </c>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
@@ -17832,10 +17992,10 @@
     </row>
     <row r="2" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:26">
       <c r="A2" s="1" t="s">
-        <v>2164</v>
+        <v>2188</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2165</v>
+        <v>2189</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -17850,7 +18010,7 @@
       <c r="M2" s="5"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1" t="s">
-        <v>2166</v>
+        <v>2190</v>
       </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
@@ -17866,10 +18026,10 @@
     </row>
     <row r="3" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:26">
       <c r="A3" s="1" t="s">
-        <v>2167</v>
+        <v>2191</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2168</v>
+        <v>2192</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -17884,7 +18044,7 @@
       <c r="M3" s="5"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1" t="s">
-        <v>2169</v>
+        <v>2193</v>
       </c>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
@@ -17900,10 +18060,10 @@
     </row>
     <row r="4" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:26">
       <c r="A4" s="1" t="s">
-        <v>2170</v>
+        <v>2194</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2171</v>
+        <v>2195</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -17918,7 +18078,7 @@
       <c r="M4" s="5"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1" t="s">
-        <v>2172</v>
+        <v>2196</v>
       </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
@@ -17934,10 +18094,10 @@
     </row>
     <row r="5" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:26">
       <c r="A5" s="1" t="s">
-        <v>2173</v>
+        <v>2197</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2174</v>
+        <v>2198</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -17952,7 +18112,7 @@
       <c r="M5" s="5"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
@@ -17968,10 +18128,10 @@
     </row>
     <row r="6" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:26">
       <c r="A6" s="1" t="s">
-        <v>2176</v>
+        <v>2200</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2177</v>
+        <v>2201</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -17986,7 +18146,7 @@
       <c r="M6" s="5"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1" t="s">
-        <v>2178</v>
+        <v>2202</v>
       </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
@@ -18002,10 +18162,10 @@
     </row>
     <row r="7" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:26">
       <c r="A7" s="1" t="s">
-        <v>2179</v>
+        <v>2203</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2180</v>
+        <v>2204</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -18020,7 +18180,7 @@
       <c r="M7" s="5"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1" t="s">
-        <v>2181</v>
+        <v>2205</v>
       </c>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
@@ -18036,10 +18196,10 @@
     </row>
     <row r="8" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:26">
       <c r="A8" s="1" t="s">
-        <v>2182</v>
+        <v>2206</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>2183</v>
+        <v>2207</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -18054,7 +18214,7 @@
       <c r="M8" s="5"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1" t="s">
-        <v>2184</v>
+        <v>2208</v>
       </c>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
@@ -18070,10 +18230,10 @@
     </row>
     <row r="9" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:26">
       <c r="A9" s="1" t="s">
-        <v>2185</v>
+        <v>2209</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2186</v>
+        <v>2210</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -18088,7 +18248,7 @@
       <c r="M9" s="5"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1" t="s">
-        <v>2187</v>
+        <v>2211</v>
       </c>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
@@ -18104,10 +18264,10 @@
     </row>
     <row r="10" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:26">
       <c r="A10" s="1" t="s">
-        <v>2188</v>
+        <v>2212</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2189</v>
+        <v>2213</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -18122,7 +18282,7 @@
       <c r="M10" s="5"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1" t="s">
-        <v>2190</v>
+        <v>2214</v>
       </c>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
@@ -18138,10 +18298,10 @@
     </row>
     <row r="11" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:26">
       <c r="A11" s="1" t="s">
-        <v>2191</v>
+        <v>2215</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2192</v>
+        <v>2216</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -18156,7 +18316,7 @@
       <c r="M11" s="5"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1" t="s">
-        <v>2193</v>
+        <v>2217</v>
       </c>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -18172,10 +18332,10 @@
     </row>
     <row r="12" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:26">
       <c r="A12" s="1" t="s">
-        <v>2194</v>
+        <v>2218</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>2195</v>
+        <v>2219</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -18190,7 +18350,7 @@
       <c r="M12" s="5"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1" t="s">
-        <v>2196</v>
+        <v>2220</v>
       </c>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
@@ -18206,10 +18366,10 @@
     </row>
     <row r="13" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:26">
       <c r="A13" s="1" t="s">
-        <v>2197</v>
+        <v>2221</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>2198</v>
+        <v>2222</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -18224,7 +18384,7 @@
       <c r="M13" s="5"/>
       <c r="N13" s="1"/>
       <c r="O13" s="1" t="s">
-        <v>2199</v>
+        <v>2223</v>
       </c>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
@@ -18240,10 +18400,10 @@
     </row>
     <row r="14" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:26">
       <c r="A14" s="1" t="s">
-        <v>2200</v>
+        <v>2224</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>2201</v>
+        <v>2225</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -18258,7 +18418,7 @@
       <c r="M14" s="5"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1" t="s">
-        <v>2202</v>
+        <v>2226</v>
       </c>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
@@ -18274,10 +18434,10 @@
     </row>
     <row r="15" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:26">
       <c r="A15" s="1" t="s">
-        <v>2203</v>
+        <v>2227</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>2204</v>
+        <v>2228</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -18292,7 +18452,7 @@
       <c r="M15" s="5"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1" t="s">
-        <v>2205</v>
+        <v>2229</v>
       </c>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
@@ -18308,10 +18468,10 @@
     </row>
     <row r="16" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:26">
       <c r="A16" s="1" t="s">
-        <v>2206</v>
+        <v>2230</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>2207</v>
+        <v>2231</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -18326,7 +18486,7 @@
       <c r="M16" s="5"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1" t="s">
-        <v>2208</v>
+        <v>2232</v>
       </c>
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
@@ -18342,10 +18502,10 @@
     </row>
     <row r="17" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:26">
       <c r="A17" s="1" t="s">
-        <v>2209</v>
+        <v>2233</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>2210</v>
+        <v>2234</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -18360,7 +18520,7 @@
       <c r="M17" s="5"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1" t="s">
-        <v>2211</v>
+        <v>2235</v>
       </c>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
@@ -18376,10 +18536,10 @@
     </row>
     <row r="18" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:26">
       <c r="A18" s="1" t="s">
-        <v>2212</v>
+        <v>2236</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>2213</v>
+        <v>2237</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -18394,7 +18554,7 @@
       <c r="M18" s="5"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1" t="s">
-        <v>2214</v>
+        <v>2238</v>
       </c>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
@@ -18410,10 +18570,10 @@
     </row>
     <row r="19" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:26">
       <c r="A19" s="1" t="s">
-        <v>2215</v>
+        <v>2239</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>2216</v>
+        <v>2240</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -18428,7 +18588,7 @@
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1" t="s">
-        <v>2217</v>
+        <v>2241</v>
       </c>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
@@ -18444,10 +18604,10 @@
     </row>
     <row r="20" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:26">
       <c r="A20" s="1" t="s">
-        <v>2218</v>
+        <v>2242</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>2219</v>
+        <v>2243</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -18462,7 +18622,7 @@
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1" t="s">
-        <v>2220</v>
+        <v>2244</v>
       </c>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
@@ -18478,10 +18638,10 @@
     </row>
     <row r="21" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:26">
       <c r="A21" s="1" t="s">
-        <v>2221</v>
+        <v>2245</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>2222</v>
+        <v>2246</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -18496,7 +18656,7 @@
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1" t="s">
-        <v>2223</v>
+        <v>2247</v>
       </c>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
@@ -18512,10 +18672,10 @@
     </row>
     <row r="22" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:26">
       <c r="A22" s="1" t="s">
-        <v>2224</v>
+        <v>2248</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>2225</v>
+        <v>2249</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -18530,7 +18690,7 @@
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
       <c r="O22" s="1" t="s">
-        <v>2226</v>
+        <v>2250</v>
       </c>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
@@ -18546,10 +18706,10 @@
     </row>
     <row r="23" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:26">
       <c r="A23" s="1" t="s">
-        <v>2227</v>
+        <v>2251</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>2228</v>
+        <v>2252</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -18564,7 +18724,7 @@
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
       <c r="O23" s="1" t="s">
-        <v>2229</v>
+        <v>2253</v>
       </c>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
@@ -18580,10 +18740,10 @@
     </row>
     <row r="24" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:26">
       <c r="A24" s="1" t="s">
-        <v>2230</v>
+        <v>2254</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>2231</v>
+        <v>2255</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -18598,7 +18758,7 @@
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1" t="s">
-        <v>2232</v>
+        <v>2256</v>
       </c>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
@@ -18614,10 +18774,10 @@
     </row>
     <row r="25" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:26">
       <c r="A25" s="1" t="s">
-        <v>2233</v>
+        <v>2257</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>2234</v>
+        <v>2258</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -18632,7 +18792,7 @@
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1" t="s">
-        <v>2235</v>
+        <v>2259</v>
       </c>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
@@ -18718,120 +18878,120 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>2236</v>
+        <v>2260</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>2237</v>
+        <v>2261</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>2238</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="2" t="s">
-        <v>2239</v>
+        <v>2263</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>2240</v>
+        <v>2264</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>2241</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="2" t="s">
-        <v>2242</v>
+        <v>2266</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>2243</v>
+        <v>2267</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>2244</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="2" t="s">
-        <v>2245</v>
+        <v>2269</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>2246</v>
+        <v>2270</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>2247</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="2" t="s">
-        <v>2248</v>
+        <v>2272</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>2249</v>
+        <v>2273</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>2250</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="2" t="s">
-        <v>2251</v>
+        <v>2275</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>2252</v>
+        <v>2276</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>2253</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="2" t="s">
-        <v>2254</v>
+        <v>2278</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>2255</v>
+        <v>2279</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>2256</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="2" t="s">
-        <v>2257</v>
+        <v>2281</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>2258</v>
+        <v>2282</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>2259</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="2" t="s">
-        <v>2260</v>
+        <v>2284</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>2261</v>
+        <v>2285</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>2262</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="2" t="s">
-        <v>2263</v>
+        <v>2287</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>2264</v>
+        <v>2288</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>2265</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="2" t="s">
-        <v>2266</v>
+        <v>2290</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>2267</v>
+        <v>2291</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>33</v>
@@ -18839,10 +18999,10 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="2" t="s">
-        <v>2268</v>
+        <v>2292</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>2269</v>
+        <v>2293</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>36</v>
@@ -18850,10 +19010,10 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="2" t="s">
-        <v>2270</v>
+        <v>2294</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>2271</v>
+        <v>2295</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>39</v>
@@ -18861,24 +19021,24 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="2" t="s">
-        <v>2272</v>
+        <v>2296</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>2243</v>
+        <v>2267</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>2273</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="2" t="s">
-        <v>2274</v>
+        <v>2298</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>2275</v>
+        <v>2299</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>2276</v>
+        <v>2300</v>
       </c>
     </row>
   </sheetData>
@@ -18966,135 +19126,135 @@
     </row>
     <row r="2" s="1" customFormat="1" spans="1:15">
       <c r="A2" s="1" t="s">
-        <v>2277</v>
+        <v>2301</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2278</v>
+        <v>2302</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>2279</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:15">
       <c r="A3" s="1" t="s">
-        <v>2280</v>
+        <v>2304</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2281</v>
+        <v>2305</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>2282</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1"/>
     <row r="5" spans="1:15">
       <c r="A5" s="2" t="s">
-        <v>2283</v>
+        <v>2307</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>2284</v>
+        <v>2308</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>2285</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="2" t="s">
-        <v>2286</v>
+        <v>2310</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>2287</v>
+        <v>2311</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>2288</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="2" t="s">
-        <v>2289</v>
+        <v>2313</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>2290</v>
+        <v>2314</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>2291</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="2" t="s">
-        <v>2292</v>
+        <v>2316</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>2293</v>
+        <v>2317</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>2294</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="2" t="s">
-        <v>2295</v>
+        <v>2319</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>2296</v>
+        <v>2320</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>2297</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="2" t="s">
-        <v>2298</v>
+        <v>2322</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>2299</v>
+        <v>2323</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>2300</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="2" t="s">
-        <v>2301</v>
+        <v>2325</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>2302</v>
+        <v>2326</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>2303</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="2" t="s">
-        <v>2304</v>
+        <v>2328</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>2305</v>
+        <v>2329</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>2306</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="2" t="s">
-        <v>2307</v>
+        <v>2331</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>2308</v>
+        <v>2332</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>2309</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="2" t="s">
-        <v>2310</v>
+        <v>2334</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>2311</v>
+        <v>2335</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>2312</v>
+        <v>2336</v>
       </c>
     </row>
   </sheetData>
